--- a/src/legalizador/legalizador.xlsx
+++ b/src/legalizador/legalizador.xlsx
@@ -2080,7 +2080,7 @@
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>El Usuario no corresponde con el KIT activado a traves de IVR</t>
         </is>
       </c>
     </row>

--- a/src/legalizador/legalizador.xlsx
+++ b/src/legalizador/legalizador.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyectos\TeamComunicaciones\automatizadorteam\src\legalizador\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D3183A-24FC-4F95-8CF8-279FB26DCC2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64E266FA-C212-46C7-87B4-A93EBB176EB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6885" yWindow="2865" windowWidth="14985" windowHeight="11670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2985" yWindow="2985" windowWidth="22875" windowHeight="10905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t>idvendedor</t>
   </si>
@@ -55,133 +55,19 @@
     <t>Mensaje</t>
   </si>
   <si>
+    <t xml:space="preserve"> 702309942351</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 353167580614683</t>
+  </si>
+  <si>
     <t>Inver Group Ant SAS</t>
   </si>
   <si>
-    <t>MORE</t>
-  </si>
-  <si>
-    <t>JHONNY DE JESUS</t>
-  </si>
-  <si>
-    <t>602207212821</t>
-  </si>
-  <si>
-    <t>702408783563</t>
-  </si>
-  <si>
-    <t>702403038145</t>
-  </si>
-  <si>
-    <t>502502454769</t>
-  </si>
-  <si>
-    <t>602206207886</t>
-  </si>
-  <si>
-    <t>502507843645</t>
-  </si>
-  <si>
-    <t>602002212069</t>
-  </si>
-  <si>
-    <t>602002212140</t>
-  </si>
-  <si>
-    <t>702309969237</t>
-  </si>
-  <si>
-    <t>502508009070</t>
-  </si>
-  <si>
-    <t>602303897368</t>
-  </si>
-  <si>
-    <t>602207057086</t>
-  </si>
-  <si>
-    <t>353270602155402</t>
-  </si>
-  <si>
-    <t>865201077067161</t>
-  </si>
-  <si>
-    <t>868796073300927</t>
-  </si>
-  <si>
-    <t>354825494912670</t>
-  </si>
-  <si>
-    <t>867070070914903</t>
-  </si>
-  <si>
-    <t>860319073322581</t>
-  </si>
-  <si>
-    <t>860515077875348</t>
-  </si>
-  <si>
-    <t>860515077988943</t>
-  </si>
-  <si>
-    <t>354825494712344</t>
-  </si>
-  <si>
-    <t>354825494568654</t>
-  </si>
-  <si>
-    <t>865776070230981</t>
-  </si>
-  <si>
-    <t>354825494805056</t>
-  </si>
-  <si>
-    <t>3144118536</t>
-  </si>
-  <si>
-    <t>3213872029</t>
-  </si>
-  <si>
-    <t>3123199608</t>
-  </si>
-  <si>
-    <t>3138210779</t>
-  </si>
-  <si>
-    <t>3223767940</t>
-  </si>
-  <si>
-    <t>3216185595</t>
-  </si>
-  <si>
-    <t>3116571670</t>
-  </si>
-  <si>
-    <t>3116150691</t>
-  </si>
-  <si>
-    <t>3228295820</t>
-  </si>
-  <si>
-    <t>3133313862</t>
-  </si>
-  <si>
-    <t>3138318414</t>
-  </si>
-  <si>
-    <t>3138659164</t>
-  </si>
-  <si>
-    <t>900721484</t>
-  </si>
-  <si>
-    <t>1045690047</t>
-  </si>
-  <si>
     <t>nit</t>
   </si>
   <si>
-    <t>cc</t>
+    <t>error</t>
   </si>
 </sst>
 </file>
@@ -237,12 +123,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -545,17 +430,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="11.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="18.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="9.140625" style="2"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -593,315 +469,32 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+      <c r="A2">
         <v>1000443105</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2">
+        <v>3229002081</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2">
+        <v>900721484</v>
+      </c>
+      <c r="H2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>1000443105</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="K2" t="s">
         <v>15</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>1000443105</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>1000443105</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>1000443105</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>1000443105</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>1000443105</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <v>1000443105</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>1000443105</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>1000443105</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>1000443105</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
-        <v>1000443105</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/src/legalizador/legalizador.xlsx
+++ b/src/legalizador/legalizador.xlsx
@@ -1,96 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyectos\TeamComunicaciones\automatizadorteam\src\legalizador\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64E266FA-C212-46C7-87B4-A93EBB176EB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="2985" yWindow="2985" windowWidth="22875" windowHeight="10905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
-  <si>
-    <t>idvendedor</t>
-  </si>
-  <si>
-    <t>iccid</t>
-  </si>
-  <si>
-    <t>imei</t>
-  </si>
-  <si>
-    <t>min</t>
-  </si>
-  <si>
-    <t>apellido</t>
-  </si>
-  <si>
-    <t>nombre</t>
-  </si>
-  <si>
-    <t>cedula</t>
-  </si>
-  <si>
-    <t>tipodoc</t>
-  </si>
-  <si>
-    <t>Unnamed: 8</t>
-  </si>
-  <si>
-    <t>Min</t>
-  </si>
-  <si>
-    <t>Mensaje</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 702309942351</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 353167580614683</t>
-  </si>
-  <si>
-    <t>Inver Group Ant SAS</t>
-  </si>
-  <si>
-    <t>nit</t>
-  </si>
-  <si>
-    <t>error</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -105,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -429,73 +420,2526 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1000443105</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2">
-        <v>3229002081</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2">
-        <v>900721484</v>
-      </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" t="s">
-        <v>15</v>
-      </c>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>idvendedor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>iccid</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>imei</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>apellido</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>nombre</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cedula</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tipodoc</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 8</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Mensaje</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 502507460346</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061767437613</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3102155883</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SUAREZ</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ESTEBAN</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1036662206</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>* Su Solicitud fue enviada satisfactoriamente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 502507715741</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354825494970512</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3213576147</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SUAREZ</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ESTEBAN</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1036662206</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 502507708386</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 866649078168801</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3214893913</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>* Su Solicitud fue enviada satisfactoriamente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 502507460043</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061767435690</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3102118445</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>El Kit ya se encuentra registrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308217693</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 356019770477123</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3125684772</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>* Su Solicitud fue enviada satisfactoriamente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 502507459964</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 866215079202708</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3102100455</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>* Su Solicitud fue enviada satisfactoriamente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 502507460252</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061767436623</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3102116799</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>El Kit ya se encuentra registrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 502507459967</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 866215079253560</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3102099558</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>El Kit ya se encuentra registrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 502507713523</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 866649078460620</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3214069470</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>El Kit ya se encuentra registrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 702408808503</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 864403070346508</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3132445841</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>NATALY</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1012323671</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>El Kit ya se encuentra registrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247375</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061767760014</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3209653944</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>El Kit ya se encuentra registrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247291</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061767754264</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3209623956</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247281</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061767752961</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>3209620210</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>El Kit ya se encuentra registrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247333</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061767759131</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3209626560</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247297</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061767756442</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>3209636447</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>El Kit ya se encuentra registrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247280</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061767752276</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3209618956</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>El Kit ya se encuentra registrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247399</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061768013769</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3209644049</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>El Kit ya se encuentra registrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247412</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061768016739</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>3209652742</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247290</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061767754090</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>3209621489</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>El Kit ya se encuentra registrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247400</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061768014650</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3209646484</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247323</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061767759123</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>3209672767</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>El Kit ya se encuentra registrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247292</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061767754918</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>3209625214</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>El Kit ya se encuentra registrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247288</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061767753662</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>3209621511</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247317</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061767757713</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>3209625323</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>El Kit ya se encuentra registrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247415</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061768017521</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>3209655205</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>El Kit ya se encuentra registrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247376</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061767760030</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>3209657643</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247419</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061769092168</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>3209661527</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>El Kit ya se encuentra registrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247416</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061769085550</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>3209655252</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>El Kit ya se encuentra registrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247301</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061767757572</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>3209637692</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247314</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061767757689</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>3209640188</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247409</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061768015574</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>3209649010</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>El Kit ya se encuentra registrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 502507489513</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061765534668</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>3132678585</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247364</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061767759172</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>3209652665</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>El Kit ya se encuentra registrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247341</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061767759156</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>3209647645</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247411</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061768016317</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>3209651488</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>El Kit ya se encuentra registrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247338</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061767759149</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>3209645204</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 502507430283</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061767754462</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>3115578293</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>El Kit ya se encuentra registrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247295</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061767756236</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>3209632697</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247377</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061767760055</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>3209657697</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>El Kit ya se encuentra registrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247385</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061768009536</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>3209634030</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>El Kit ya se encuentra registrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247398</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061768013215</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>3209642776</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247410</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061768015962</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>3209650254</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>El Kit ya se encuentra registrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 502507723145</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601898200</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>3114563410</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247384</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061768009122</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>3209662694</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247417</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061769088018</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>3209657719</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 502507430289</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061767756046</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>3115592392</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 502507430322</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061768008090</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>3115584709</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247390</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061768012480</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>3209640256</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247389</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061768012423</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>3209671570</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247414</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061768017166</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>3209652763</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247386</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061768012308</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>3209635284</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247418</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061769090790</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>3209658976</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247392</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061768012597</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>3209641510</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247379</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061768008983</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>3209631494</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247403</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061768014999</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>3209674013</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247293</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061767755014</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>3209622817</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247378</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061768008702</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>3209658946</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247296</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061767756277</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>3209633928</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247345</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354061767759164</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>3209650152</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>JHONNY DE JESUS</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>1045690047</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>1000443105</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602308247249</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 864152061036277</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>3209644924</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>CASTRO</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>DORA</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>20492428</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/src/legalizador/legalizador.xlsx
+++ b/src/legalizador/legalizador.xlsx
@@ -1,138 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Camilo Jaramillo\source\repos\Team\AutomatizadorSoftware2\src\legalizador\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE04F674-2C72-4FB9-A10E-2AE20FC7E1A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
-  <si>
-    <t>idvendedor</t>
-  </si>
-  <si>
-    <t>iccid</t>
-  </si>
-  <si>
-    <t>imei</t>
-  </si>
-  <si>
-    <t>min</t>
-  </si>
-  <si>
-    <t>apellido</t>
-  </si>
-  <si>
-    <t>nombre</t>
-  </si>
-  <si>
-    <t>cedula</t>
-  </si>
-  <si>
-    <t>tipodoc</t>
-  </si>
-  <si>
-    <t>Unnamed: 8</t>
-  </si>
-  <si>
-    <t>Min</t>
-  </si>
-  <si>
-    <t>Mensaje</t>
-  </si>
-  <si>
-    <t>cc</t>
-  </si>
-  <si>
-    <t>702309963968</t>
-  </si>
-  <si>
-    <t>353167580712768</t>
-  </si>
-  <si>
-    <t>3144546245</t>
-  </si>
-  <si>
-    <t>LIBERO</t>
-  </si>
-  <si>
-    <t>MOBIL</t>
-  </si>
-  <si>
-    <t>8323453</t>
-  </si>
-  <si>
-    <t>602307891395</t>
-  </si>
-  <si>
-    <t>356310850576698</t>
-  </si>
-  <si>
-    <t>3229150414</t>
-  </si>
-  <si>
-    <t>Inver Group Ant SAS</t>
-  </si>
-  <si>
-    <t>900721484</t>
-  </si>
-  <si>
-    <t>nit</t>
-  </si>
-  <si>
-    <t>702308746062</t>
-  </si>
-  <si>
-    <t>354825494711049</t>
-  </si>
-  <si>
-    <t>3115362192</t>
-  </si>
-  <si>
-    <t>CALDERA</t>
-  </si>
-  <si>
-    <t>CARLOS EMIRO</t>
-  </si>
-  <si>
-    <t>099491934</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -147,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -471,134 +420,195 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.7109375" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>idvendedor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>iccid</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>imei</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>apellido</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>nombre</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cedula</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tipodoc</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 8</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Mensaje</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2">
+      <c r="A2" t="n">
         <v>1036962271</v>
       </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" t="s">
-        <v>11</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 702309963968</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353167580712768</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3144546245</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>LIBERO</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>MOBIL</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>8323453</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>La consulta demograficos no arrojo informacion para este cliente</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3">
+    <row r="3">
+      <c r="A3" t="n">
         <v>1036962271</v>
       </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" t="s">
-        <v>23</v>
-      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 602307891395</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 356310850576698</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3229150414</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Inver Group Ant SAS</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Inver Group Ant SAS</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>900721484</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>nit</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4">
+    <row r="4">
+      <c r="A4" t="n">
         <v>1036962271</v>
       </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" t="s">
-        <v>11</v>
-      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 702308746062</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 354825494711049</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3115362192</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CALDERA</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CARLOS EMIRO</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>99491934</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/src/legalizador/legalizador.xlsx
+++ b/src/legalizador/legalizador.xlsx
@@ -1,37 +1,126 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Camilo Jaramillo\source\repos\Team\AutomatizadorSoftware2\src\legalizador\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8EFB68F-5E88-488A-A939-0F4335AB3C5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
+  <si>
+    <t>idvendedor</t>
+  </si>
+  <si>
+    <t>iccid</t>
+  </si>
+  <si>
+    <t>imei</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>apellido</t>
+  </si>
+  <si>
+    <t>nombre</t>
+  </si>
+  <si>
+    <t>cedula</t>
+  </si>
+  <si>
+    <t>tipodoc</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Mensaje</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602707483328</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 353167580615276</t>
+  </si>
+  <si>
+    <t>CALDERA</t>
+  </si>
+  <si>
+    <t>CARLOS EMIRO</t>
+  </si>
+  <si>
+    <t>cc</t>
+  </si>
+  <si>
+    <t>error</t>
+  </si>
+  <si>
+    <t>La consulta demograficos no arrojo informacion para este cliente</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 502502446466</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 867957076658387</t>
+  </si>
+  <si>
+    <t>Inver Group Ant SAS</t>
+  </si>
+  <si>
+    <t>nit</t>
+  </si>
+  <si>
+    <t>procesado</t>
+  </si>
+  <si>
+    <t>* Su Solicitud fue enviada satisfactoriamente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 502502446542</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 867957075012768</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +135,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,195 +459,140 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>idvendedor</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>iccid</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>imei</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>apellido</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>nombre</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>cedula</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>tipodoc</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 8</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Mensaje</t>
-        </is>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>1036962271</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 702309963968</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 353167580712768</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>3144546245</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>LIBERO</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>MOBIL</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>8323453</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>cc</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>La consulta demograficos no arrojo informacion para este cliente</t>
-        </is>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2">
+        <v>3228858415</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2">
+        <v>99491934</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>1036962271</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 602307891395</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 356310850576698</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>3229150414</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Inver Group Ant SAS</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Inver Group Ant SAS</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3">
+        <v>3144656124</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3">
         <v>900721484</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>nit</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>1036962271</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 702308746062</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 354825494711049</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>3115362192</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>CALDERA</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>CARLOS EMIRO</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>99491934</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>cc</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4">
+        <v>3143194955</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4">
+        <v>900721484</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" t="s">
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/src/legalizador/legalizador.xlsx
+++ b/src/legalizador/legalizador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Camilo Jaramillo\source\repos\Team\AutomatizadorSoftware2\src\legalizador\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8EFB68F-5E88-488A-A939-0F4335AB3C5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C0C02F-765D-40FC-A7A3-E011C0C32F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="300">
   <si>
     <t>idvendedor</t>
   </si>
@@ -55,49 +55,871 @@
     <t>Mensaje</t>
   </si>
   <si>
-    <t xml:space="preserve"> 602707483328</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 353167580615276</t>
-  </si>
-  <si>
-    <t>CALDERA</t>
-  </si>
-  <si>
-    <t>CARLOS EMIRO</t>
+    <t xml:space="preserve"> 502502446487</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 867957072097762</t>
+  </si>
+  <si>
+    <t>Inver Group Ant SAS</t>
+  </si>
+  <si>
+    <t>nit</t>
+  </si>
+  <si>
+    <t>Procesado</t>
+  </si>
+  <si>
+    <t>* Su Solicitud fue enviada satisfactoriamente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 502502446471</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 867957072062329</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 502502446575</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 867957072059663</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 502502446560</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 867957075025729</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 502502446500</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 867957072095741</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 502502446507</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 867957071716305</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 502502446485</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 867957074957161</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 502502446578</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 867957071710142</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 502502446490</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 867957072080040</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 502502446484</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 867957074936561</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 502502446569</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 867957078338269</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602409046414</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 356933582486660</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 502502446563</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 867957075026842</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 502502446497</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 867957074979207</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602307873017</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 860515079861486</t>
+  </si>
+  <si>
+    <t>ESPINOSA</t>
+  </si>
+  <si>
+    <t>DIANA PAOLA</t>
   </si>
   <si>
     <t>cc</t>
   </si>
   <si>
+    <t xml:space="preserve"> 602706057347</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 862805077302122</t>
+  </si>
+  <si>
+    <t>ESPITIA</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602307006456</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 862805076899284</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 702409755537</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 353384833521033</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602502083039</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 862805077007507</t>
+  </si>
+  <si>
+    <t>FABRA</t>
+  </si>
+  <si>
+    <t>ALVERT</t>
+  </si>
+  <si>
     <t>error</t>
   </si>
   <si>
     <t>La consulta demograficos no arrojo informacion para este cliente</t>
   </si>
   <si>
-    <t xml:space="preserve"> 502502446466</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 867957076658387</t>
-  </si>
-  <si>
-    <t>Inver Group Ant SAS</t>
-  </si>
-  <si>
-    <t>nit</t>
-  </si>
-  <si>
-    <t>procesado</t>
-  </si>
-  <si>
-    <t>* Su Solicitud fue enviada satisfactoriamente.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 502502446542</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 867957075012768</t>
+    <t xml:space="preserve"> 602708150848</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 862805070785141</t>
+  </si>
+  <si>
+    <t>BOMPAT</t>
+  </si>
+  <si>
+    <t>David Manuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602607348182</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 860185070057003</t>
+  </si>
+  <si>
+    <t>Error validación: Plan invalido</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602206133880</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 867070070198887</t>
+  </si>
+  <si>
+    <t>CREDIMOVIL JJ SAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602206134011</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 867070070207183</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 702312590348</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 866572076725440</t>
+  </si>
+  <si>
+    <t>Error validación: Los datos del Kit NO corresponden</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602206231662</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 867070075075460</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 702403316197</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 863015070121946</t>
+  </si>
+  <si>
+    <t>COOPERATIVA DE TRANSPORTADORES SAN ANTONIO COOTRASANA</t>
+  </si>
+  <si>
+    <t>Error validación: El Kit ya se encuentra registrado</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602710973789</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 353167580558955</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>LEONARDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602207051790</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 862124078920720</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602207057425</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 353384833520282</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602207243942</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 353270602137525</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602206130849</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 867070070207324</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 502502445687</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 353270601889134</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602207044499</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 353384835308504</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602207045374</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 353384835309247</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602409041820</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 353384836902701</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602609652271</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 354825494641238</t>
+  </si>
+  <si>
+    <t>MORE</t>
+  </si>
+  <si>
+    <t>JHONNY DE JESUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 702409755026</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 861108060357125</t>
+  </si>
+  <si>
+    <t>CLAUDIA MARCELA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 702408794252</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 358082860752951</t>
+  </si>
+  <si>
+    <t>RUBIANO</t>
+  </si>
+  <si>
+    <t>PATRICIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602411292181</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 865776071153240</t>
+  </si>
+  <si>
+    <t>JOSE DUVAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602502083260</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 354208767944268</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>ESTEBAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 502507835046</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 354825494901004</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602711012432</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 354208765083010</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 502507725315</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 354208768248271</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 702408999746</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 358082860746383</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>NILTON</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602002235292</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 359681341265662</t>
+  </si>
+  <si>
+    <t>ARGANEZ</t>
+  </si>
+  <si>
+    <t>HERNAN DARIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602002222403</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 351769535722644</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>Luis Fernando</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602705612174</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 357429534200811</t>
+  </si>
+  <si>
+    <t>MACHADO</t>
+  </si>
+  <si>
+    <t>LAUDACIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602402163139</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 865503064687665</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>RICHARD KILPATRY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602402308646</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 351479729437724</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 502502036381</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 351769531901739</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 702403003644</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 868149070313545</t>
+  </si>
+  <si>
+    <t>ACELAS</t>
+  </si>
+  <si>
+    <t>JUAN FERNANDO</t>
+  </si>
+  <si>
+    <t>Error en procesamiento - transacción saltada</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 702403515879</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 869018072836366</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>SERGIO ANTONIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 702409797438</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 868149070722489</t>
+  </si>
+  <si>
+    <t>AGUIRRE</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 702403465166</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 350078587832272</t>
+  </si>
+  <si>
+    <t>ALIAN</t>
+  </si>
+  <si>
+    <t>DIANI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 702408353046</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 868149070924119</t>
+  </si>
+  <si>
+    <t>ALVARADO</t>
+  </si>
+  <si>
+    <t>LEIDY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 702408999367</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 868149070207358</t>
+  </si>
+  <si>
+    <t>SHIRLEY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 702408999337</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 865991075001507</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>JOSE DANIEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 702408992526</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 869018078607647</t>
+  </si>
+  <si>
+    <t>ANHELI SAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602407045924</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 865991075920003</t>
+  </si>
+  <si>
+    <t>ARAMBURO</t>
+  </si>
+  <si>
+    <t>CRISTIAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 702408987798</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 869018076951609</t>
+  </si>
+  <si>
+    <t>ARAQUE</t>
+  </si>
+  <si>
+    <t>DIEGO CAMILO</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 702409417392</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 351646935273354</t>
+  </si>
+  <si>
+    <t>ARBOLEDA</t>
+  </si>
+  <si>
+    <t>LAURA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 702403409916</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 865991076073240</t>
+  </si>
+  <si>
+    <t>ARDILA</t>
+  </si>
+  <si>
+    <t>YIMIN FRANCISCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 702408987791</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 862998074121288</t>
+  </si>
+  <si>
+    <t>ARENAS</t>
+  </si>
+  <si>
+    <t>FERNANDO FELIPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602307019781</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 353167580564219</t>
+  </si>
+  <si>
+    <t>RUTH MARIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 702408999360</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 868149070468661</t>
+  </si>
+  <si>
+    <t>MANUEL ALEJANDRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 702309289581</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 356214263089150</t>
+  </si>
+  <si>
+    <t>JUAN MANUEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 702409787812</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 868149070228255</t>
+  </si>
+  <si>
+    <t>ARIEL</t>
+  </si>
+  <si>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 702403515895</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 869018072759584</t>
+  </si>
+  <si>
+    <t>ARISTIZABAL</t>
+  </si>
+  <si>
+    <t>NISBENY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602407040254</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 869018076933441</t>
+  </si>
+  <si>
+    <t>MATEO MIGUEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 702409054474</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 869807073658005</t>
+  </si>
+  <si>
+    <t>ARTEAGA</t>
+  </si>
+  <si>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 702408987786</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 862998074126345</t>
+  </si>
+  <si>
+    <t>AVENDAÑO</t>
+  </si>
+  <si>
+    <t>FABIAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 702409762464</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 869018076978164</t>
+  </si>
+  <si>
+    <t>AYALA</t>
+  </si>
+  <si>
+    <t>FERNANDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 702408999143</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 865201070442163</t>
+  </si>
+  <si>
+    <t>MARCOLFA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 702409750160</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 351646935290721</t>
+  </si>
+  <si>
+    <t>BACON GROUP SAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 702409541157</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 350399470283039</t>
+  </si>
+  <si>
+    <t>BAENA</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 702408987579</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 869018076945429</t>
+  </si>
+  <si>
+    <t>BASTIDAS</t>
+  </si>
+  <si>
+    <t>ALBIERO</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602309814304</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 352432217774776</t>
+  </si>
+  <si>
+    <t>BEDOYA</t>
+  </si>
+  <si>
+    <t>EUCARIS DE JESUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602309814291</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 354061761666506</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602309814277</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 356019770476638</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602309829948</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 352432217867281</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602309814309</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 354061768011953</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602309814280</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 356019771719374</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602309814301</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 356019770674703</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602309814285</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 354061769862115</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602309814308</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 354061761411382</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602309829950</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 352432215306175</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602309814276</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 354061769856265</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602309814290</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 352432214733031</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602309814295</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 356019772678710</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602309814306</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 356019771271566</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602309814302</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 356019771272424</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602309814279</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 356019771715091</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602309814298</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 356019772679221</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602309814305</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 352432215309617</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602309814258</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 354061767409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602309814249</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 354061767412764</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602309814243</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 354061769549860</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602309814299</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 356019772678496</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602309814254</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 356019771716495</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 602309814310</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 356019772677209</t>
   </si>
 </sst>
 </file>
@@ -460,8 +1282,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -509,25 +1338,25 @@
         <v>12</v>
       </c>
       <c r="D2">
-        <v>3228858415</v>
+        <v>3144747650</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
       </c>
       <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2">
+        <v>900721484</v>
+      </c>
+      <c r="H2" t="s">
         <v>14</v>
       </c>
-      <c r="G2">
-        <v>99491934</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
       <c r="J2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -535,31 +1364,31 @@
         <v>1036962271</v>
       </c>
       <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
       <c r="D3">
-        <v>3144656124</v>
+        <v>3144647370</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G3">
         <v>900721484</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K3" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -567,31 +1396,3135 @@
         <v>1036962271</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D4">
-        <v>3143194955</v>
+        <v>3143153983</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>900721484</v>
       </c>
       <c r="H4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1036962271</v>
+      </c>
+      <c r="B5" t="s">
         <v>21</v>
       </c>
-      <c r="J4" t="s">
+      <c r="C5" t="s">
         <v>22</v>
       </c>
-      <c r="K4" t="s">
+      <c r="D5">
+        <v>3143198869</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5">
+        <v>900721484</v>
+      </c>
+      <c r="H5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1036962271</v>
+      </c>
+      <c r="B6" t="s">
         <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6">
+        <v>3144751560</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>900721484</v>
+      </c>
+      <c r="H6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>1036962271</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7">
+        <v>3144721374</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7">
+        <v>900721484</v>
+      </c>
+      <c r="H7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J7" t="s">
+        <v>15</v>
+      </c>
+      <c r="K7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>1036962271</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8">
+        <v>3144723640</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8">
+        <v>900721484</v>
+      </c>
+      <c r="H8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J8" t="s">
+        <v>15</v>
+      </c>
+      <c r="K8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>1036962271</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9">
+        <v>3143185663</v>
+      </c>
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9">
+        <v>900721484</v>
+      </c>
+      <c r="H9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>1036962271</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10">
+        <v>3144721213</v>
+      </c>
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10">
+        <v>900721484</v>
+      </c>
+      <c r="H10" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" t="s">
+        <v>15</v>
+      </c>
+      <c r="K10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>1036962271</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11">
+        <v>3144719823</v>
+      </c>
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11">
+        <v>900721484</v>
+      </c>
+      <c r="H11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" t="s">
+        <v>15</v>
+      </c>
+      <c r="K11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>1036962271</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12">
+        <v>3143188036</v>
+      </c>
+      <c r="E12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12">
+        <v>900721484</v>
+      </c>
+      <c r="H12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" t="s">
+        <v>15</v>
+      </c>
+      <c r="K12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>1036962271</v>
+      </c>
+      <c r="B13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13">
+        <v>3142012661</v>
+      </c>
+      <c r="E13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13">
+        <v>900721484</v>
+      </c>
+      <c r="H13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" t="s">
+        <v>15</v>
+      </c>
+      <c r="K13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>1036962271</v>
+      </c>
+      <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14">
+        <v>3143164051</v>
+      </c>
+      <c r="E14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14">
+        <v>900721484</v>
+      </c>
+      <c r="H14" t="s">
+        <v>14</v>
+      </c>
+      <c r="J14" t="s">
+        <v>15</v>
+      </c>
+      <c r="K14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>1036962271</v>
+      </c>
+      <c r="B15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15">
+        <v>3144737635</v>
+      </c>
+      <c r="E15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15">
+        <v>900721484</v>
+      </c>
+      <c r="H15" t="s">
+        <v>14</v>
+      </c>
+      <c r="J15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>1036962271</v>
+      </c>
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16">
+        <v>3115479358</v>
+      </c>
+      <c r="E16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16">
+        <v>1044505415</v>
+      </c>
+      <c r="H16" t="s">
+        <v>47</v>
+      </c>
+      <c r="J16" t="s">
+        <v>15</v>
+      </c>
+      <c r="K16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>1036962271</v>
+      </c>
+      <c r="B17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17">
+        <v>3127318559</v>
+      </c>
+      <c r="E17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G17">
+        <v>71986451</v>
+      </c>
+      <c r="H17" t="s">
+        <v>47</v>
+      </c>
+      <c r="J17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>1036962271</v>
+      </c>
+      <c r="B18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18">
+        <v>3102330089</v>
+      </c>
+      <c r="E18" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18">
+        <v>71986451</v>
+      </c>
+      <c r="H18" t="s">
+        <v>47</v>
+      </c>
+      <c r="J18" t="s">
+        <v>15</v>
+      </c>
+      <c r="K18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>1036962271</v>
+      </c>
+      <c r="B19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19">
+        <v>3142735383</v>
+      </c>
+      <c r="E19" t="s">
+        <v>56</v>
+      </c>
+      <c r="F19" t="s">
+        <v>57</v>
+      </c>
+      <c r="G19">
+        <v>1007466318</v>
+      </c>
+      <c r="H19" t="s">
+        <v>47</v>
+      </c>
+      <c r="J19" t="s">
+        <v>15</v>
+      </c>
+      <c r="K19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>1036962271</v>
+      </c>
+      <c r="B20" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20">
+        <v>3127327663</v>
+      </c>
+      <c r="E20" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20" t="s">
+        <v>61</v>
+      </c>
+      <c r="G20">
+        <v>8166106</v>
+      </c>
+      <c r="H20" t="s">
+        <v>47</v>
+      </c>
+      <c r="J20" t="s">
+        <v>62</v>
+      </c>
+      <c r="K20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>1036962271</v>
+      </c>
+      <c r="B21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21">
+        <v>3108960186</v>
+      </c>
+      <c r="E21" t="s">
+        <v>66</v>
+      </c>
+      <c r="F21" t="s">
+        <v>67</v>
+      </c>
+      <c r="G21">
+        <v>1126427587</v>
+      </c>
+      <c r="H21" t="s">
+        <v>47</v>
+      </c>
+      <c r="J21" t="s">
+        <v>62</v>
+      </c>
+      <c r="K21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>1036962271</v>
+      </c>
+      <c r="B22" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22">
+        <v>3219018648</v>
+      </c>
+      <c r="E22" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22">
+        <v>900721484</v>
+      </c>
+      <c r="H22" t="s">
+        <v>14</v>
+      </c>
+      <c r="J22" t="s">
+        <v>62</v>
+      </c>
+      <c r="K22" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>1036962271</v>
+      </c>
+      <c r="B23" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23">
+        <v>3227168363</v>
+      </c>
+      <c r="E23" t="s">
+        <v>73</v>
+      </c>
+      <c r="F23" t="s">
+        <v>73</v>
+      </c>
+      <c r="G23">
+        <v>9016460294</v>
+      </c>
+      <c r="H23" t="s">
+        <v>14</v>
+      </c>
+      <c r="J23" t="s">
+        <v>15</v>
+      </c>
+      <c r="K23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>1036962271</v>
+      </c>
+      <c r="B24" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24">
+        <v>3227128540</v>
+      </c>
+      <c r="E24" t="s">
+        <v>73</v>
+      </c>
+      <c r="F24" t="s">
+        <v>73</v>
+      </c>
+      <c r="G24">
+        <v>9016460294</v>
+      </c>
+      <c r="H24" t="s">
+        <v>14</v>
+      </c>
+      <c r="J24" t="s">
+        <v>15</v>
+      </c>
+      <c r="K24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>1036962271</v>
+      </c>
+      <c r="B25" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" t="s">
+        <v>77</v>
+      </c>
+      <c r="D25">
+        <v>3105600643</v>
+      </c>
+      <c r="E25" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25">
+        <v>900721484</v>
+      </c>
+      <c r="H25" t="s">
+        <v>14</v>
+      </c>
+      <c r="J25" t="s">
+        <v>62</v>
+      </c>
+      <c r="K25" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>1036962271</v>
+      </c>
+      <c r="B26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26">
+        <v>3123535587</v>
+      </c>
+      <c r="E26" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26">
+        <v>900721484</v>
+      </c>
+      <c r="H26" t="s">
+        <v>14</v>
+      </c>
+      <c r="J26" t="s">
+        <v>62</v>
+      </c>
+      <c r="K26" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>1036962271</v>
+      </c>
+      <c r="B27" t="s">
+        <v>81</v>
+      </c>
+      <c r="C27" t="s">
+        <v>82</v>
+      </c>
+      <c r="D27">
+        <v>3134607936</v>
+      </c>
+      <c r="E27" t="s">
+        <v>83</v>
+      </c>
+      <c r="F27" t="s">
+        <v>83</v>
+      </c>
+      <c r="G27">
+        <v>8909060331</v>
+      </c>
+      <c r="H27" t="s">
+        <v>14</v>
+      </c>
+      <c r="J27" t="s">
+        <v>62</v>
+      </c>
+      <c r="K27" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>1036962271</v>
+      </c>
+      <c r="B28" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" t="s">
+        <v>86</v>
+      </c>
+      <c r="D28">
+        <v>3115601038</v>
+      </c>
+      <c r="E28" t="s">
+        <v>87</v>
+      </c>
+      <c r="F28" t="s">
+        <v>88</v>
+      </c>
+      <c r="G28">
+        <v>6910978</v>
+      </c>
+      <c r="H28" t="s">
+        <v>47</v>
+      </c>
+      <c r="J28" t="s">
+        <v>62</v>
+      </c>
+      <c r="K28" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>1036962271</v>
+      </c>
+      <c r="B29" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29" t="s">
+        <v>90</v>
+      </c>
+      <c r="D29">
+        <v>3208490656</v>
+      </c>
+      <c r="E29" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" t="s">
+        <v>13</v>
+      </c>
+      <c r="G29">
+        <v>900721484</v>
+      </c>
+      <c r="H29" t="s">
+        <v>14</v>
+      </c>
+      <c r="J29" t="s">
+        <v>62</v>
+      </c>
+      <c r="K29" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>1036962271</v>
+      </c>
+      <c r="B30" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" t="s">
+        <v>92</v>
+      </c>
+      <c r="D30">
+        <v>3212440859</v>
+      </c>
+      <c r="E30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30">
+        <v>900721484</v>
+      </c>
+      <c r="H30" t="s">
+        <v>14</v>
+      </c>
+      <c r="J30" t="s">
+        <v>62</v>
+      </c>
+      <c r="K30" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>1036962271</v>
+      </c>
+      <c r="B31" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" t="s">
+        <v>94</v>
+      </c>
+      <c r="D31">
+        <v>3224009485</v>
+      </c>
+      <c r="E31" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31">
+        <v>900721484</v>
+      </c>
+      <c r="H31" t="s">
+        <v>14</v>
+      </c>
+      <c r="J31" t="s">
+        <v>62</v>
+      </c>
+      <c r="K31" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>1036962271</v>
+      </c>
+      <c r="B32" t="s">
+        <v>95</v>
+      </c>
+      <c r="C32" t="s">
+        <v>96</v>
+      </c>
+      <c r="D32">
+        <v>3227219798</v>
+      </c>
+      <c r="E32" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32">
+        <v>900721484</v>
+      </c>
+      <c r="H32" t="s">
+        <v>14</v>
+      </c>
+      <c r="J32" t="s">
+        <v>62</v>
+      </c>
+      <c r="K32" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>1036962271</v>
+      </c>
+      <c r="B33" t="s">
+        <v>97</v>
+      </c>
+      <c r="C33" t="s">
+        <v>98</v>
+      </c>
+      <c r="D33">
+        <v>3136180226</v>
+      </c>
+      <c r="E33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33">
+        <v>900721484</v>
+      </c>
+      <c r="H33" t="s">
+        <v>14</v>
+      </c>
+      <c r="J33" t="s">
+        <v>62</v>
+      </c>
+      <c r="K33" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>1036962271</v>
+      </c>
+      <c r="B34" t="s">
+        <v>99</v>
+      </c>
+      <c r="C34" t="s">
+        <v>100</v>
+      </c>
+      <c r="D34">
+        <v>3134712612</v>
+      </c>
+      <c r="E34" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34">
+        <v>900721484</v>
+      </c>
+      <c r="H34" t="s">
+        <v>14</v>
+      </c>
+      <c r="J34" t="s">
+        <v>62</v>
+      </c>
+      <c r="K34" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>1036962271</v>
+      </c>
+      <c r="B35" t="s">
+        <v>101</v>
+      </c>
+      <c r="C35" t="s">
+        <v>102</v>
+      </c>
+      <c r="D35">
+        <v>3138398183</v>
+      </c>
+      <c r="E35" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35">
+        <v>900721484</v>
+      </c>
+      <c r="H35" t="s">
+        <v>14</v>
+      </c>
+      <c r="J35" t="s">
+        <v>62</v>
+      </c>
+      <c r="K35" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>1036962271</v>
+      </c>
+      <c r="B36" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36" t="s">
+        <v>104</v>
+      </c>
+      <c r="D36">
+        <v>3229043615</v>
+      </c>
+      <c r="E36" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36">
+        <v>900721484</v>
+      </c>
+      <c r="H36" t="s">
+        <v>14</v>
+      </c>
+      <c r="J36" t="s">
+        <v>62</v>
+      </c>
+      <c r="K36" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>1036962271</v>
+      </c>
+      <c r="B37" t="s">
+        <v>105</v>
+      </c>
+      <c r="C37" t="s">
+        <v>106</v>
+      </c>
+      <c r="D37">
+        <v>3105808129</v>
+      </c>
+      <c r="E37" t="s">
+        <v>107</v>
+      </c>
+      <c r="F37" t="s">
+        <v>108</v>
+      </c>
+      <c r="G37">
+        <v>1045690047</v>
+      </c>
+      <c r="H37" t="s">
+        <v>47</v>
+      </c>
+      <c r="J37" t="s">
+        <v>62</v>
+      </c>
+      <c r="K37" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>1036962271</v>
+      </c>
+      <c r="B38" t="s">
+        <v>109</v>
+      </c>
+      <c r="C38" t="s">
+        <v>110</v>
+      </c>
+      <c r="D38">
+        <v>3132452675</v>
+      </c>
+      <c r="E38" t="s">
+        <v>56</v>
+      </c>
+      <c r="F38" t="s">
+        <v>111</v>
+      </c>
+      <c r="G38">
+        <v>31793646</v>
+      </c>
+      <c r="H38" t="s">
+        <v>47</v>
+      </c>
+      <c r="J38" t="s">
+        <v>62</v>
+      </c>
+      <c r="K38" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>1036962271</v>
+      </c>
+      <c r="B39" t="s">
+        <v>112</v>
+      </c>
+      <c r="C39" t="s">
+        <v>113</v>
+      </c>
+      <c r="D39">
+        <v>3209256454</v>
+      </c>
+      <c r="E39" t="s">
+        <v>114</v>
+      </c>
+      <c r="F39" t="s">
+        <v>115</v>
+      </c>
+      <c r="G39">
+        <v>52346196</v>
+      </c>
+      <c r="H39" t="s">
+        <v>47</v>
+      </c>
+      <c r="J39" t="s">
+        <v>62</v>
+      </c>
+      <c r="K39" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>1036962271</v>
+      </c>
+      <c r="B40" t="s">
+        <v>116</v>
+      </c>
+      <c r="C40" t="s">
+        <v>117</v>
+      </c>
+      <c r="D40">
+        <v>3223742869</v>
+      </c>
+      <c r="E40" t="s">
+        <v>114</v>
+      </c>
+      <c r="F40" t="s">
+        <v>118</v>
+      </c>
+      <c r="G40">
+        <v>1110582527</v>
+      </c>
+      <c r="H40" t="s">
+        <v>47</v>
+      </c>
+      <c r="J40" t="s">
+        <v>62</v>
+      </c>
+      <c r="K40" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>1036962271</v>
+      </c>
+      <c r="B41" t="s">
+        <v>119</v>
+      </c>
+      <c r="C41" t="s">
+        <v>120</v>
+      </c>
+      <c r="D41">
+        <v>3117414267</v>
+      </c>
+      <c r="E41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F41" t="s">
+        <v>122</v>
+      </c>
+      <c r="G41">
+        <v>1036662206</v>
+      </c>
+      <c r="H41" t="s">
+        <v>47</v>
+      </c>
+      <c r="J41" t="s">
+        <v>62</v>
+      </c>
+      <c r="K41" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>1036962271</v>
+      </c>
+      <c r="B42" t="s">
+        <v>123</v>
+      </c>
+      <c r="C42" t="s">
+        <v>124</v>
+      </c>
+      <c r="D42">
+        <v>3205583810</v>
+      </c>
+      <c r="E42" t="s">
+        <v>121</v>
+      </c>
+      <c r="F42" t="s">
+        <v>122</v>
+      </c>
+      <c r="G42">
+        <v>1036662206</v>
+      </c>
+      <c r="H42" t="s">
+        <v>47</v>
+      </c>
+      <c r="J42" t="s">
+        <v>62</v>
+      </c>
+      <c r="K42" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>1036962271</v>
+      </c>
+      <c r="B43" t="s">
+        <v>125</v>
+      </c>
+      <c r="C43" t="s">
+        <v>126</v>
+      </c>
+      <c r="D43">
+        <v>3214397004</v>
+      </c>
+      <c r="E43" t="s">
+        <v>121</v>
+      </c>
+      <c r="F43" t="s">
+        <v>122</v>
+      </c>
+      <c r="G43">
+        <v>1036662206</v>
+      </c>
+      <c r="H43" t="s">
+        <v>47</v>
+      </c>
+      <c r="J43" t="s">
+        <v>62</v>
+      </c>
+      <c r="K43" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>1036962271</v>
+      </c>
+      <c r="B44" t="s">
+        <v>127</v>
+      </c>
+      <c r="C44" t="s">
+        <v>128</v>
+      </c>
+      <c r="D44">
+        <v>3124923245</v>
+      </c>
+      <c r="E44" t="s">
+        <v>121</v>
+      </c>
+      <c r="F44" t="s">
+        <v>122</v>
+      </c>
+      <c r="G44">
+        <v>1036662206</v>
+      </c>
+      <c r="H44" t="s">
+        <v>47</v>
+      </c>
+      <c r="J44" t="s">
+        <v>62</v>
+      </c>
+      <c r="K44" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>1036962271</v>
+      </c>
+      <c r="B45" t="s">
+        <v>129</v>
+      </c>
+      <c r="C45" t="s">
+        <v>130</v>
+      </c>
+      <c r="D45">
+        <v>3132958250</v>
+      </c>
+      <c r="E45" t="s">
+        <v>131</v>
+      </c>
+      <c r="F45" t="s">
+        <v>132</v>
+      </c>
+      <c r="G45">
+        <v>1114338477</v>
+      </c>
+      <c r="H45" t="s">
+        <v>47</v>
+      </c>
+      <c r="J45" t="s">
+        <v>62</v>
+      </c>
+      <c r="K45" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>1036962271</v>
+      </c>
+      <c r="B46" t="s">
+        <v>133</v>
+      </c>
+      <c r="C46" t="s">
+        <v>134</v>
+      </c>
+      <c r="D46">
+        <v>3114560295</v>
+      </c>
+      <c r="E46" t="s">
+        <v>135</v>
+      </c>
+      <c r="F46" t="s">
+        <v>136</v>
+      </c>
+      <c r="G46">
+        <v>8127552</v>
+      </c>
+      <c r="H46" t="s">
+        <v>47</v>
+      </c>
+      <c r="J46" t="s">
+        <v>62</v>
+      </c>
+      <c r="K46" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>1036962271</v>
+      </c>
+      <c r="B47" t="s">
+        <v>137</v>
+      </c>
+      <c r="C47" t="s">
+        <v>138</v>
+      </c>
+      <c r="D47">
+        <v>3115538464</v>
+      </c>
+      <c r="E47" t="s">
+        <v>139</v>
+      </c>
+      <c r="F47" t="s">
+        <v>140</v>
+      </c>
+      <c r="G47">
+        <v>98578191</v>
+      </c>
+      <c r="H47" t="s">
+        <v>47</v>
+      </c>
+      <c r="J47" t="s">
+        <v>15</v>
+      </c>
+      <c r="K47" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>1036962271</v>
+      </c>
+      <c r="B48" t="s">
+        <v>141</v>
+      </c>
+      <c r="C48" t="s">
+        <v>142</v>
+      </c>
+      <c r="D48">
+        <v>3123239107</v>
+      </c>
+      <c r="E48" t="s">
+        <v>143</v>
+      </c>
+      <c r="F48" t="s">
+        <v>144</v>
+      </c>
+      <c r="G48">
+        <v>26292754</v>
+      </c>
+      <c r="H48" t="s">
+        <v>47</v>
+      </c>
+      <c r="J48" t="s">
+        <v>15</v>
+      </c>
+      <c r="K48" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>1036962271</v>
+      </c>
+      <c r="B49" t="s">
+        <v>145</v>
+      </c>
+      <c r="C49" t="s">
+        <v>146</v>
+      </c>
+      <c r="D49">
+        <v>3114506293</v>
+      </c>
+      <c r="E49" t="s">
+        <v>147</v>
+      </c>
+      <c r="F49" t="s">
+        <v>148</v>
+      </c>
+      <c r="G49">
+        <v>79881341</v>
+      </c>
+      <c r="H49" t="s">
+        <v>47</v>
+      </c>
+      <c r="J49" t="s">
+        <v>15</v>
+      </c>
+      <c r="K49" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>1036962271</v>
+      </c>
+      <c r="B50" t="s">
+        <v>149</v>
+      </c>
+      <c r="C50" t="s">
+        <v>150</v>
+      </c>
+      <c r="D50">
+        <v>3114570918</v>
+      </c>
+      <c r="E50" t="s">
+        <v>121</v>
+      </c>
+      <c r="F50" t="s">
+        <v>122</v>
+      </c>
+      <c r="G50">
+        <v>1036662206</v>
+      </c>
+      <c r="H50" t="s">
+        <v>47</v>
+      </c>
+      <c r="J50" t="s">
+        <v>15</v>
+      </c>
+      <c r="K50" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>1036962271</v>
+      </c>
+      <c r="B51" t="s">
+        <v>151</v>
+      </c>
+      <c r="C51" t="s">
+        <v>152</v>
+      </c>
+      <c r="D51">
+        <v>3114541472</v>
+      </c>
+      <c r="E51" t="s">
+        <v>121</v>
+      </c>
+      <c r="F51" t="s">
+        <v>122</v>
+      </c>
+      <c r="G51">
+        <v>1036662206</v>
+      </c>
+      <c r="H51" t="s">
+        <v>47</v>
+      </c>
+      <c r="J51" t="s">
+        <v>15</v>
+      </c>
+      <c r="K51" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>1036962271</v>
+      </c>
+      <c r="B52" t="s">
+        <v>153</v>
+      </c>
+      <c r="C52" t="s">
+        <v>154</v>
+      </c>
+      <c r="D52">
+        <v>3222957644</v>
+      </c>
+      <c r="E52" t="s">
+        <v>155</v>
+      </c>
+      <c r="F52" t="s">
+        <v>156</v>
+      </c>
+      <c r="G52">
+        <v>1100952680</v>
+      </c>
+      <c r="H52" t="s">
+        <v>47</v>
+      </c>
+      <c r="J52" t="s">
+        <v>62</v>
+      </c>
+      <c r="K52" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>1036962271</v>
+      </c>
+      <c r="B53" t="s">
+        <v>158</v>
+      </c>
+      <c r="C53" t="s">
+        <v>159</v>
+      </c>
+      <c r="D53">
+        <v>3212284630</v>
+      </c>
+      <c r="E53" t="s">
+        <v>160</v>
+      </c>
+      <c r="F53" t="s">
+        <v>161</v>
+      </c>
+      <c r="G53">
+        <v>1098754521</v>
+      </c>
+      <c r="H53" t="s">
+        <v>47</v>
+      </c>
+      <c r="J53" t="s">
+        <v>15</v>
+      </c>
+      <c r="K53" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>1036962271</v>
+      </c>
+      <c r="B54" t="s">
+        <v>162</v>
+      </c>
+      <c r="C54" t="s">
+        <v>163</v>
+      </c>
+      <c r="D54">
+        <v>3222348653</v>
+      </c>
+      <c r="E54" t="s">
+        <v>164</v>
+      </c>
+      <c r="F54" t="s">
+        <v>165</v>
+      </c>
+      <c r="G54">
+        <v>1194714152</v>
+      </c>
+      <c r="H54" t="s">
+        <v>47</v>
+      </c>
+      <c r="J54" t="s">
+        <v>15</v>
+      </c>
+      <c r="K54" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>1036962271</v>
+      </c>
+      <c r="B55" t="s">
+        <v>166</v>
+      </c>
+      <c r="C55" t="s">
+        <v>167</v>
+      </c>
+      <c r="D55">
+        <v>3202906393</v>
+      </c>
+      <c r="E55" t="s">
+        <v>168</v>
+      </c>
+      <c r="F55" t="s">
+        <v>169</v>
+      </c>
+      <c r="G55">
+        <v>1063275522</v>
+      </c>
+      <c r="H55" t="s">
+        <v>47</v>
+      </c>
+      <c r="J55" t="s">
+        <v>15</v>
+      </c>
+      <c r="K55" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>1036962271</v>
+      </c>
+      <c r="B56" t="s">
+        <v>170</v>
+      </c>
+      <c r="C56" t="s">
+        <v>171</v>
+      </c>
+      <c r="D56">
+        <v>3222484456</v>
+      </c>
+      <c r="E56" t="s">
+        <v>172</v>
+      </c>
+      <c r="F56" t="s">
+        <v>173</v>
+      </c>
+      <c r="G56">
+        <v>1085226658</v>
+      </c>
+      <c r="H56" t="s">
+        <v>47</v>
+      </c>
+      <c r="J56" t="s">
+        <v>15</v>
+      </c>
+      <c r="K56" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>1036962271</v>
+      </c>
+      <c r="B57" t="s">
+        <v>174</v>
+      </c>
+      <c r="C57" t="s">
+        <v>175</v>
+      </c>
+      <c r="D57">
+        <v>3214624400</v>
+      </c>
+      <c r="E57" t="s">
+        <v>139</v>
+      </c>
+      <c r="F57" t="s">
+        <v>176</v>
+      </c>
+      <c r="G57">
+        <v>1140838593</v>
+      </c>
+      <c r="H57" t="s">
+        <v>47</v>
+      </c>
+      <c r="J57" t="s">
+        <v>15</v>
+      </c>
+      <c r="K57" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>1036962271</v>
+      </c>
+      <c r="B58" t="s">
+        <v>177</v>
+      </c>
+      <c r="C58" t="s">
+        <v>178</v>
+      </c>
+      <c r="D58">
+        <v>3202683634</v>
+      </c>
+      <c r="E58" t="s">
+        <v>179</v>
+      </c>
+      <c r="F58" t="s">
+        <v>180</v>
+      </c>
+      <c r="G58">
+        <v>1045080933</v>
+      </c>
+      <c r="H58" t="s">
+        <v>47</v>
+      </c>
+      <c r="J58" t="s">
+        <v>15</v>
+      </c>
+      <c r="K58" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>1036962271</v>
+      </c>
+      <c r="B59" t="s">
+        <v>181</v>
+      </c>
+      <c r="C59" t="s">
+        <v>182</v>
+      </c>
+      <c r="D59">
+        <v>3138437570</v>
+      </c>
+      <c r="E59" t="s">
+        <v>183</v>
+      </c>
+      <c r="F59" t="s">
+        <v>183</v>
+      </c>
+      <c r="G59">
+        <v>9014252214</v>
+      </c>
+      <c r="H59" t="s">
+        <v>14</v>
+      </c>
+      <c r="J59" t="s">
+        <v>15</v>
+      </c>
+      <c r="K59" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>1036962271</v>
+      </c>
+      <c r="B60" t="s">
+        <v>184</v>
+      </c>
+      <c r="C60" t="s">
+        <v>185</v>
+      </c>
+      <c r="D60">
+        <v>3113026437</v>
+      </c>
+      <c r="E60" t="s">
+        <v>186</v>
+      </c>
+      <c r="F60" t="s">
+        <v>187</v>
+      </c>
+      <c r="G60">
+        <v>1144089224</v>
+      </c>
+      <c r="H60" t="s">
+        <v>47</v>
+      </c>
+      <c r="J60" t="s">
+        <v>15</v>
+      </c>
+      <c r="K60" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>1036962271</v>
+      </c>
+      <c r="B61" t="s">
+        <v>188</v>
+      </c>
+      <c r="C61" t="s">
+        <v>189</v>
+      </c>
+      <c r="D61">
+        <v>3208238385</v>
+      </c>
+      <c r="E61" t="s">
+        <v>190</v>
+      </c>
+      <c r="F61" t="s">
+        <v>191</v>
+      </c>
+      <c r="G61">
+        <v>1057583529</v>
+      </c>
+      <c r="H61" t="s">
+        <v>47</v>
+      </c>
+      <c r="J61" t="s">
+        <v>15</v>
+      </c>
+      <c r="K61" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>1036962271</v>
+      </c>
+      <c r="B62" t="s">
+        <v>192</v>
+      </c>
+      <c r="C62" t="s">
+        <v>193</v>
+      </c>
+      <c r="D62">
+        <v>3103242107</v>
+      </c>
+      <c r="E62" t="s">
+        <v>194</v>
+      </c>
+      <c r="F62" t="s">
+        <v>195</v>
+      </c>
+      <c r="G62">
+        <v>1007559100</v>
+      </c>
+      <c r="H62" t="s">
+        <v>47</v>
+      </c>
+      <c r="J62" t="s">
+        <v>15</v>
+      </c>
+      <c r="K62" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>1036962271</v>
+      </c>
+      <c r="B63" t="s">
+        <v>196</v>
+      </c>
+      <c r="C63" t="s">
+        <v>197</v>
+      </c>
+      <c r="D63">
+        <v>3213364905</v>
+      </c>
+      <c r="E63" t="s">
+        <v>198</v>
+      </c>
+      <c r="F63" t="s">
+        <v>199</v>
+      </c>
+      <c r="G63">
+        <v>88268709</v>
+      </c>
+      <c r="H63" t="s">
+        <v>47</v>
+      </c>
+      <c r="J63" t="s">
+        <v>15</v>
+      </c>
+      <c r="K63" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>1036962271</v>
+      </c>
+      <c r="B64" t="s">
+        <v>200</v>
+      </c>
+      <c r="C64" t="s">
+        <v>201</v>
+      </c>
+      <c r="D64">
+        <v>3209192810</v>
+      </c>
+      <c r="E64" t="s">
+        <v>202</v>
+      </c>
+      <c r="F64" t="s">
+        <v>203</v>
+      </c>
+      <c r="G64">
+        <v>1098617271</v>
+      </c>
+      <c r="H64" t="s">
+        <v>47</v>
+      </c>
+      <c r="J64" t="s">
+        <v>62</v>
+      </c>
+      <c r="K64" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>1036962271</v>
+      </c>
+      <c r="B65" t="s">
+        <v>204</v>
+      </c>
+      <c r="C65" t="s">
+        <v>205</v>
+      </c>
+      <c r="D65">
+        <v>3228932058</v>
+      </c>
+      <c r="E65" t="s">
+        <v>202</v>
+      </c>
+      <c r="F65" t="s">
+        <v>206</v>
+      </c>
+      <c r="G65">
+        <v>21737811</v>
+      </c>
+      <c r="H65" t="s">
+        <v>47</v>
+      </c>
+      <c r="J65" t="s">
+        <v>15</v>
+      </c>
+      <c r="K65" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>1036962271</v>
+      </c>
+      <c r="B66" t="s">
+        <v>207</v>
+      </c>
+      <c r="C66" t="s">
+        <v>208</v>
+      </c>
+      <c r="D66">
+        <v>3222959099</v>
+      </c>
+      <c r="E66" t="s">
+        <v>147</v>
+      </c>
+      <c r="F66" t="s">
+        <v>209</v>
+      </c>
+      <c r="G66">
+        <v>1000759005</v>
+      </c>
+      <c r="H66" t="s">
+        <v>47</v>
+      </c>
+      <c r="J66" t="s">
+        <v>15</v>
+      </c>
+      <c r="K66" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>1036962271</v>
+      </c>
+      <c r="B67" t="s">
+        <v>210</v>
+      </c>
+      <c r="C67" t="s">
+        <v>211</v>
+      </c>
+      <c r="D67">
+        <v>3112477627</v>
+      </c>
+      <c r="E67" t="s">
+        <v>147</v>
+      </c>
+      <c r="F67" t="s">
+        <v>212</v>
+      </c>
+      <c r="G67">
+        <v>1035972905</v>
+      </c>
+      <c r="H67" t="s">
+        <v>47</v>
+      </c>
+      <c r="J67" t="s">
+        <v>15</v>
+      </c>
+      <c r="K67" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>1036962271</v>
+      </c>
+      <c r="B68" t="s">
+        <v>213</v>
+      </c>
+      <c r="C68" t="s">
+        <v>214</v>
+      </c>
+      <c r="D68">
+        <v>3214662289</v>
+      </c>
+      <c r="E68" t="s">
+        <v>215</v>
+      </c>
+      <c r="F68" t="s">
+        <v>216</v>
+      </c>
+      <c r="G68">
+        <v>79521600</v>
+      </c>
+      <c r="H68" t="s">
+        <v>47</v>
+      </c>
+      <c r="J68" t="s">
+        <v>62</v>
+      </c>
+      <c r="K68" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>1036962271</v>
+      </c>
+      <c r="B69" t="s">
+        <v>217</v>
+      </c>
+      <c r="C69" t="s">
+        <v>218</v>
+      </c>
+      <c r="D69">
+        <v>3222308627</v>
+      </c>
+      <c r="E69" t="s">
+        <v>219</v>
+      </c>
+      <c r="F69" t="s">
+        <v>220</v>
+      </c>
+      <c r="G69">
+        <v>1005719083</v>
+      </c>
+      <c r="H69" t="s">
+        <v>47</v>
+      </c>
+      <c r="J69" t="s">
+        <v>15</v>
+      </c>
+      <c r="K69" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>1036962271</v>
+      </c>
+      <c r="B70" t="s">
+        <v>221</v>
+      </c>
+      <c r="C70" t="s">
+        <v>222</v>
+      </c>
+      <c r="D70">
+        <v>3103086730</v>
+      </c>
+      <c r="E70" t="s">
+        <v>219</v>
+      </c>
+      <c r="F70" t="s">
+        <v>223</v>
+      </c>
+      <c r="G70">
+        <v>11519405794</v>
+      </c>
+      <c r="H70" t="s">
+        <v>47</v>
+      </c>
+      <c r="J70" t="s">
+        <v>62</v>
+      </c>
+      <c r="K70" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>1036962271</v>
+      </c>
+      <c r="B71" t="s">
+        <v>224</v>
+      </c>
+      <c r="C71" t="s">
+        <v>225</v>
+      </c>
+      <c r="D71">
+        <v>3148391652</v>
+      </c>
+      <c r="E71" t="s">
+        <v>226</v>
+      </c>
+      <c r="F71" t="s">
+        <v>227</v>
+      </c>
+      <c r="G71">
+        <v>10940614</v>
+      </c>
+      <c r="H71" t="s">
+        <v>47</v>
+      </c>
+      <c r="J71" t="s">
+        <v>15</v>
+      </c>
+      <c r="K71" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>1036962271</v>
+      </c>
+      <c r="B72" t="s">
+        <v>228</v>
+      </c>
+      <c r="C72" t="s">
+        <v>229</v>
+      </c>
+      <c r="D72">
+        <v>3209130896</v>
+      </c>
+      <c r="E72" t="s">
+        <v>230</v>
+      </c>
+      <c r="F72" t="s">
+        <v>231</v>
+      </c>
+      <c r="G72">
+        <v>10487987</v>
+      </c>
+      <c r="H72" t="s">
+        <v>47</v>
+      </c>
+      <c r="J72" t="s">
+        <v>15</v>
+      </c>
+      <c r="K72" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>1036962271</v>
+      </c>
+      <c r="B73" t="s">
+        <v>232</v>
+      </c>
+      <c r="C73" t="s">
+        <v>233</v>
+      </c>
+      <c r="D73">
+        <v>3143597424</v>
+      </c>
+      <c r="E73" t="s">
+        <v>234</v>
+      </c>
+      <c r="F73" t="s">
+        <v>235</v>
+      </c>
+      <c r="G73">
+        <v>1071164225</v>
+      </c>
+      <c r="H73" t="s">
+        <v>47</v>
+      </c>
+      <c r="J73" t="s">
+        <v>15</v>
+      </c>
+      <c r="K73" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>1036962271</v>
+      </c>
+      <c r="B74" t="s">
+        <v>236</v>
+      </c>
+      <c r="C74" t="s">
+        <v>237</v>
+      </c>
+      <c r="D74">
+        <v>3204781627</v>
+      </c>
+      <c r="E74" t="s">
+        <v>234</v>
+      </c>
+      <c r="F74" t="s">
+        <v>238</v>
+      </c>
+      <c r="G74">
+        <v>63251354</v>
+      </c>
+      <c r="H74" t="s">
+        <v>47</v>
+      </c>
+      <c r="J74" t="s">
+        <v>15</v>
+      </c>
+      <c r="K74" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>1036962271</v>
+      </c>
+      <c r="B75" t="s">
+        <v>239</v>
+      </c>
+      <c r="C75" t="s">
+        <v>240</v>
+      </c>
+      <c r="D75">
+        <v>3224538557</v>
+      </c>
+      <c r="E75" t="s">
+        <v>241</v>
+      </c>
+      <c r="F75" t="s">
+        <v>241</v>
+      </c>
+      <c r="G75">
+        <v>9017317976</v>
+      </c>
+      <c r="H75" t="s">
+        <v>14</v>
+      </c>
+      <c r="J75" t="s">
+        <v>15</v>
+      </c>
+      <c r="K75" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>1036962271</v>
+      </c>
+      <c r="B76" t="s">
+        <v>242</v>
+      </c>
+      <c r="C76" t="s">
+        <v>243</v>
+      </c>
+      <c r="D76">
+        <v>3205696141</v>
+      </c>
+      <c r="E76" t="s">
+        <v>244</v>
+      </c>
+      <c r="F76" t="s">
+        <v>245</v>
+      </c>
+      <c r="G76">
+        <v>1039705662</v>
+      </c>
+      <c r="H76" t="s">
+        <v>47</v>
+      </c>
+      <c r="J76" t="s">
+        <v>15</v>
+      </c>
+      <c r="K76" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>1036962271</v>
+      </c>
+      <c r="B77" t="s">
+        <v>246</v>
+      </c>
+      <c r="C77" t="s">
+        <v>247</v>
+      </c>
+      <c r="D77">
+        <v>3108637668</v>
+      </c>
+      <c r="E77" t="s">
+        <v>248</v>
+      </c>
+      <c r="F77" t="s">
+        <v>249</v>
+      </c>
+      <c r="G77">
+        <v>1067714980</v>
+      </c>
+      <c r="H77" t="s">
+        <v>47</v>
+      </c>
+      <c r="J77" t="s">
+        <v>15</v>
+      </c>
+      <c r="K77" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>1036962271</v>
+      </c>
+      <c r="B78" t="s">
+        <v>250</v>
+      </c>
+      <c r="C78" t="s">
+        <v>251</v>
+      </c>
+      <c r="D78">
+        <v>3138506597</v>
+      </c>
+      <c r="E78" t="s">
+        <v>252</v>
+      </c>
+      <c r="F78" t="s">
+        <v>253</v>
+      </c>
+      <c r="G78">
+        <v>21463753</v>
+      </c>
+      <c r="H78" t="s">
+        <v>47</v>
+      </c>
+      <c r="J78" t="s">
+        <v>15</v>
+      </c>
+      <c r="K78" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>1036962271</v>
+      </c>
+      <c r="B79" t="s">
+        <v>254</v>
+      </c>
+      <c r="C79" t="s">
+        <v>255</v>
+      </c>
+      <c r="D79">
+        <v>3138498253</v>
+      </c>
+      <c r="E79" t="s">
+        <v>252</v>
+      </c>
+      <c r="F79" t="s">
+        <v>253</v>
+      </c>
+      <c r="G79">
+        <v>21463753</v>
+      </c>
+      <c r="H79" t="s">
+        <v>47</v>
+      </c>
+      <c r="J79" t="s">
+        <v>15</v>
+      </c>
+      <c r="K79" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>1036962271</v>
+      </c>
+      <c r="B80" t="s">
+        <v>256</v>
+      </c>
+      <c r="C80" t="s">
+        <v>257</v>
+      </c>
+      <c r="D80">
+        <v>3138503830</v>
+      </c>
+      <c r="E80" t="s">
+        <v>252</v>
+      </c>
+      <c r="F80" t="s">
+        <v>253</v>
+      </c>
+      <c r="G80">
+        <v>21463753</v>
+      </c>
+      <c r="H80" t="s">
+        <v>47</v>
+      </c>
+      <c r="J80" t="s">
+        <v>15</v>
+      </c>
+      <c r="K80" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>1036962271</v>
+      </c>
+      <c r="B81" t="s">
+        <v>258</v>
+      </c>
+      <c r="C81" t="s">
+        <v>259</v>
+      </c>
+      <c r="D81">
+        <v>3124071572</v>
+      </c>
+      <c r="E81" t="s">
+        <v>252</v>
+      </c>
+      <c r="F81" t="s">
+        <v>253</v>
+      </c>
+      <c r="G81">
+        <v>21463753</v>
+      </c>
+      <c r="H81" t="s">
+        <v>47</v>
+      </c>
+      <c r="J81" t="s">
+        <v>15</v>
+      </c>
+      <c r="K81" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>1036962271</v>
+      </c>
+      <c r="B82" t="s">
+        <v>260</v>
+      </c>
+      <c r="C82" t="s">
+        <v>261</v>
+      </c>
+      <c r="D82">
+        <v>3134275302</v>
+      </c>
+      <c r="E82" t="s">
+        <v>252</v>
+      </c>
+      <c r="F82" t="s">
+        <v>253</v>
+      </c>
+      <c r="G82">
+        <v>21463753</v>
+      </c>
+      <c r="H82" t="s">
+        <v>47</v>
+      </c>
+      <c r="J82" t="s">
+        <v>15</v>
+      </c>
+      <c r="K82" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>1036962271</v>
+      </c>
+      <c r="B83" t="s">
+        <v>262</v>
+      </c>
+      <c r="C83" t="s">
+        <v>263</v>
+      </c>
+      <c r="D83">
+        <v>3138490915</v>
+      </c>
+      <c r="E83" t="s">
+        <v>252</v>
+      </c>
+      <c r="F83" t="s">
+        <v>253</v>
+      </c>
+      <c r="G83">
+        <v>21463753</v>
+      </c>
+      <c r="H83" t="s">
+        <v>47</v>
+      </c>
+      <c r="J83" t="s">
+        <v>15</v>
+      </c>
+      <c r="K83" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>1036962271</v>
+      </c>
+      <c r="B84" t="s">
+        <v>264</v>
+      </c>
+      <c r="C84" t="s">
+        <v>265</v>
+      </c>
+      <c r="D84">
+        <v>3138469987</v>
+      </c>
+      <c r="E84" t="s">
+        <v>252</v>
+      </c>
+      <c r="F84" t="s">
+        <v>253</v>
+      </c>
+      <c r="G84">
+        <v>21463753</v>
+      </c>
+      <c r="H84" t="s">
+        <v>47</v>
+      </c>
+      <c r="J84" t="s">
+        <v>15</v>
+      </c>
+      <c r="K84" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>1036962271</v>
+      </c>
+      <c r="B85" t="s">
+        <v>266</v>
+      </c>
+      <c r="C85" t="s">
+        <v>267</v>
+      </c>
+      <c r="D85">
+        <v>3138494651</v>
+      </c>
+      <c r="E85" t="s">
+        <v>252</v>
+      </c>
+      <c r="F85" t="s">
+        <v>253</v>
+      </c>
+      <c r="G85">
+        <v>21463753</v>
+      </c>
+      <c r="H85" t="s">
+        <v>47</v>
+      </c>
+      <c r="J85" t="s">
+        <v>15</v>
+      </c>
+      <c r="K85" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>1036962271</v>
+      </c>
+      <c r="B86" t="s">
+        <v>268</v>
+      </c>
+      <c r="C86" t="s">
+        <v>269</v>
+      </c>
+      <c r="D86">
+        <v>3134272788</v>
+      </c>
+      <c r="E86" t="s">
+        <v>252</v>
+      </c>
+      <c r="F86" t="s">
+        <v>253</v>
+      </c>
+      <c r="G86">
+        <v>21463753</v>
+      </c>
+      <c r="H86" t="s">
+        <v>47</v>
+      </c>
+      <c r="J86" t="s">
+        <v>15</v>
+      </c>
+      <c r="K86" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>1036962271</v>
+      </c>
+      <c r="B87" t="s">
+        <v>270</v>
+      </c>
+      <c r="C87" t="s">
+        <v>271</v>
+      </c>
+      <c r="D87">
+        <v>3124076565</v>
+      </c>
+      <c r="E87" t="s">
+        <v>252</v>
+      </c>
+      <c r="F87" t="s">
+        <v>253</v>
+      </c>
+      <c r="G87">
+        <v>21463753</v>
+      </c>
+      <c r="H87" t="s">
+        <v>47</v>
+      </c>
+      <c r="J87" t="s">
+        <v>15</v>
+      </c>
+      <c r="K87" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>1036962271</v>
+      </c>
+      <c r="B88" t="s">
+        <v>272</v>
+      </c>
+      <c r="C88" t="s">
+        <v>273</v>
+      </c>
+      <c r="D88">
+        <v>3138503805</v>
+      </c>
+      <c r="E88" t="s">
+        <v>252</v>
+      </c>
+      <c r="F88" t="s">
+        <v>253</v>
+      </c>
+      <c r="G88">
+        <v>21463753</v>
+      </c>
+      <c r="H88" t="s">
+        <v>47</v>
+      </c>
+      <c r="J88" t="s">
+        <v>15</v>
+      </c>
+      <c r="K88" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>1036962271</v>
+      </c>
+      <c r="B89" t="s">
+        <v>274</v>
+      </c>
+      <c r="C89" t="s">
+        <v>275</v>
+      </c>
+      <c r="D89">
+        <v>3138497226</v>
+      </c>
+      <c r="E89" t="s">
+        <v>252</v>
+      </c>
+      <c r="F89" t="s">
+        <v>253</v>
+      </c>
+      <c r="G89">
+        <v>21463753</v>
+      </c>
+      <c r="H89" t="s">
+        <v>47</v>
+      </c>
+      <c r="J89" t="s">
+        <v>15</v>
+      </c>
+      <c r="K89" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>1036962271</v>
+      </c>
+      <c r="B90" t="s">
+        <v>276</v>
+      </c>
+      <c r="C90" t="s">
+        <v>277</v>
+      </c>
+      <c r="D90">
+        <v>3134294094</v>
+      </c>
+      <c r="E90" t="s">
+        <v>252</v>
+      </c>
+      <c r="F90" t="s">
+        <v>253</v>
+      </c>
+      <c r="G90">
+        <v>21463753</v>
+      </c>
+      <c r="H90" t="s">
+        <v>47</v>
+      </c>
+      <c r="J90" t="s">
+        <v>15</v>
+      </c>
+      <c r="K90" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>1036962271</v>
+      </c>
+      <c r="B91" t="s">
+        <v>278</v>
+      </c>
+      <c r="C91" t="s">
+        <v>279</v>
+      </c>
+      <c r="D91">
+        <v>3138509240</v>
+      </c>
+      <c r="E91" t="s">
+        <v>252</v>
+      </c>
+      <c r="F91" t="s">
+        <v>253</v>
+      </c>
+      <c r="G91">
+        <v>21463753</v>
+      </c>
+      <c r="H91" t="s">
+        <v>47</v>
+      </c>
+      <c r="J91" t="s">
+        <v>15</v>
+      </c>
+      <c r="K91" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>1036962271</v>
+      </c>
+      <c r="B92" t="s">
+        <v>280</v>
+      </c>
+      <c r="C92" t="s">
+        <v>281</v>
+      </c>
+      <c r="D92">
+        <v>3138510507</v>
+      </c>
+      <c r="E92" t="s">
+        <v>252</v>
+      </c>
+      <c r="F92" t="s">
+        <v>253</v>
+      </c>
+      <c r="G92">
+        <v>21463753</v>
+      </c>
+      <c r="H92" t="s">
+        <v>47</v>
+      </c>
+      <c r="J92" t="s">
+        <v>15</v>
+      </c>
+      <c r="K92" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>1036962271</v>
+      </c>
+      <c r="B93" t="s">
+        <v>282</v>
+      </c>
+      <c r="C93" t="s">
+        <v>283</v>
+      </c>
+      <c r="D93">
+        <v>3138505135</v>
+      </c>
+      <c r="E93" t="s">
+        <v>252</v>
+      </c>
+      <c r="F93" t="s">
+        <v>253</v>
+      </c>
+      <c r="G93">
+        <v>21463753</v>
+      </c>
+      <c r="H93" t="s">
+        <v>47</v>
+      </c>
+      <c r="J93" t="s">
+        <v>15</v>
+      </c>
+      <c r="K93" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>1036962271</v>
+      </c>
+      <c r="B94" t="s">
+        <v>284</v>
+      </c>
+      <c r="C94" t="s">
+        <v>285</v>
+      </c>
+      <c r="D94">
+        <v>3138464885</v>
+      </c>
+      <c r="E94" t="s">
+        <v>252</v>
+      </c>
+      <c r="F94" t="s">
+        <v>253</v>
+      </c>
+      <c r="G94">
+        <v>21463753</v>
+      </c>
+      <c r="H94" t="s">
+        <v>47</v>
+      </c>
+      <c r="J94" t="s">
+        <v>15</v>
+      </c>
+      <c r="K94" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>1036962271</v>
+      </c>
+      <c r="B95" t="s">
+        <v>286</v>
+      </c>
+      <c r="C95" t="s">
+        <v>287</v>
+      </c>
+      <c r="D95">
+        <v>3138508536</v>
+      </c>
+      <c r="E95" t="s">
+        <v>252</v>
+      </c>
+      <c r="F95" t="s">
+        <v>253</v>
+      </c>
+      <c r="G95">
+        <v>21463753</v>
+      </c>
+      <c r="H95" t="s">
+        <v>47</v>
+      </c>
+      <c r="J95" t="s">
+        <v>15</v>
+      </c>
+      <c r="K95" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <v>1036962271</v>
+      </c>
+      <c r="B96" t="s">
+        <v>288</v>
+      </c>
+      <c r="C96" t="s">
+        <v>289</v>
+      </c>
+      <c r="D96">
+        <v>3134282855</v>
+      </c>
+      <c r="E96" t="s">
+        <v>252</v>
+      </c>
+      <c r="F96" t="s">
+        <v>253</v>
+      </c>
+      <c r="G96">
+        <v>21463753</v>
+      </c>
+      <c r="H96" t="s">
+        <v>47</v>
+      </c>
+      <c r="J96" t="s">
+        <v>15</v>
+      </c>
+      <c r="K96" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>1036962271</v>
+      </c>
+      <c r="B97" t="s">
+        <v>290</v>
+      </c>
+      <c r="C97" t="s">
+        <v>291</v>
+      </c>
+      <c r="D97">
+        <v>3134280313</v>
+      </c>
+      <c r="E97" t="s">
+        <v>252</v>
+      </c>
+      <c r="F97" t="s">
+        <v>253</v>
+      </c>
+      <c r="G97">
+        <v>21463753</v>
+      </c>
+      <c r="H97" t="s">
+        <v>47</v>
+      </c>
+      <c r="J97" t="s">
+        <v>15</v>
+      </c>
+      <c r="K97" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>1036962271</v>
+      </c>
+      <c r="B98" t="s">
+        <v>292</v>
+      </c>
+      <c r="C98" t="s">
+        <v>293</v>
+      </c>
+      <c r="D98">
+        <v>3134273949</v>
+      </c>
+      <c r="E98" t="s">
+        <v>252</v>
+      </c>
+      <c r="F98" t="s">
+        <v>253</v>
+      </c>
+      <c r="G98">
+        <v>21463753</v>
+      </c>
+      <c r="H98" t="s">
+        <v>47</v>
+      </c>
+      <c r="J98" t="s">
+        <v>15</v>
+      </c>
+      <c r="K98" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <v>1036962271</v>
+      </c>
+      <c r="B99" t="s">
+        <v>294</v>
+      </c>
+      <c r="C99" t="s">
+        <v>295</v>
+      </c>
+      <c r="D99">
+        <v>3138466156</v>
+      </c>
+      <c r="E99" t="s">
+        <v>252</v>
+      </c>
+      <c r="F99" t="s">
+        <v>253</v>
+      </c>
+      <c r="G99">
+        <v>21463753</v>
+      </c>
+      <c r="H99" t="s">
+        <v>47</v>
+      </c>
+      <c r="J99" t="s">
+        <v>15</v>
+      </c>
+      <c r="K99" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>1036962271</v>
+      </c>
+      <c r="B100" t="s">
+        <v>296</v>
+      </c>
+      <c r="C100" t="s">
+        <v>297</v>
+      </c>
+      <c r="D100">
+        <v>3134281589</v>
+      </c>
+      <c r="E100" t="s">
+        <v>252</v>
+      </c>
+      <c r="F100" t="s">
+        <v>253</v>
+      </c>
+      <c r="G100">
+        <v>21463753</v>
+      </c>
+      <c r="H100" t="s">
+        <v>47</v>
+      </c>
+      <c r="J100" t="s">
+        <v>15</v>
+      </c>
+      <c r="K100" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <v>1036962271</v>
+      </c>
+      <c r="B101" t="s">
+        <v>298</v>
+      </c>
+      <c r="C101" t="s">
+        <v>299</v>
+      </c>
+      <c r="D101">
+        <v>3134277828</v>
+      </c>
+      <c r="E101" t="s">
+        <v>252</v>
+      </c>
+      <c r="F101" t="s">
+        <v>253</v>
+      </c>
+      <c r="G101">
+        <v>21463753</v>
+      </c>
+      <c r="H101" t="s">
+        <v>47</v>
+      </c>
+      <c r="J101" t="s">
+        <v>15</v>
+      </c>
+      <c r="K101" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/src/legalizador/legalizador.xlsx
+++ b/src/legalizador/legalizador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Camilo Jaramillo\source\repos\Team\AutomatizadorSoftware2\src\legalizador\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10CFC34D-86EE-405B-B3A3-1E13AE330A75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AE681FD-9B24-4162-8A3E-51B9958FC8CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1631" uniqueCount="1075">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2055" uniqueCount="1077">
   <si>
     <t>idvendedor</t>
   </si>
@@ -1522,6 +1522,9 @@
     <t>PAOLA ANDREA</t>
   </si>
   <si>
+    <t>Error validación: El Kit ya se encuentra registrado</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 602308200412</t>
   </si>
   <si>
@@ -2066,6 +2069,9 @@
   </si>
   <si>
     <t>YANIVIS YAINETH</t>
+  </si>
+  <si>
+    <t>Error validación: Plan invalido</t>
   </si>
   <si>
     <t xml:space="preserve"> 702408912212</t>
@@ -3609,6 +3615,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K293"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="57.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -5046,6 +5065,12 @@
       <c r="H45" t="s">
         <v>15</v>
       </c>
+      <c r="J45" t="s">
+        <v>16</v>
+      </c>
+      <c r="K45" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46">
@@ -5552,6 +5577,12 @@
       <c r="H61" t="s">
         <v>15</v>
       </c>
+      <c r="J61" t="s">
+        <v>16</v>
+      </c>
+      <c r="K61" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62">
@@ -5706,6 +5737,12 @@
       <c r="H66" t="s">
         <v>15</v>
       </c>
+      <c r="J66" t="s">
+        <v>16</v>
+      </c>
+      <c r="K66" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67">
@@ -6052,6 +6089,12 @@
       <c r="H77" t="s">
         <v>15</v>
       </c>
+      <c r="J77" t="s">
+        <v>16</v>
+      </c>
+      <c r="K77" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78">
@@ -6142,6 +6185,12 @@
       <c r="H80" t="s">
         <v>15</v>
       </c>
+      <c r="J80" t="s">
+        <v>16</v>
+      </c>
+      <c r="K80" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81">
@@ -6296,6 +6345,12 @@
       <c r="H85" t="s">
         <v>15</v>
       </c>
+      <c r="J85" t="s">
+        <v>16</v>
+      </c>
+      <c r="K85" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86">
@@ -6386,6 +6441,12 @@
       <c r="H88" t="s">
         <v>15</v>
       </c>
+      <c r="J88" t="s">
+        <v>16</v>
+      </c>
+      <c r="K88" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89">
@@ -6412,6 +6473,12 @@
       <c r="H89" t="s">
         <v>15</v>
       </c>
+      <c r="J89" t="s">
+        <v>16</v>
+      </c>
+      <c r="K89" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90">
@@ -6438,6 +6505,12 @@
       <c r="H90" t="s">
         <v>15</v>
       </c>
+      <c r="J90" t="s">
+        <v>16</v>
+      </c>
+      <c r="K90" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91">
@@ -6464,6 +6537,12 @@
       <c r="H91" t="s">
         <v>15</v>
       </c>
+      <c r="J91" t="s">
+        <v>16</v>
+      </c>
+      <c r="K91" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92">
@@ -6490,6 +6569,12 @@
       <c r="H92" t="s">
         <v>15</v>
       </c>
+      <c r="J92" t="s">
+        <v>16</v>
+      </c>
+      <c r="K92" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93">
@@ -6516,6 +6601,12 @@
       <c r="H93" t="s">
         <v>15</v>
       </c>
+      <c r="J93" t="s">
+        <v>16</v>
+      </c>
+      <c r="K93" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94">
@@ -6542,6 +6633,12 @@
       <c r="H94" t="s">
         <v>15</v>
       </c>
+      <c r="J94" t="s">
+        <v>16</v>
+      </c>
+      <c r="K94" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95">
@@ -6568,6 +6665,12 @@
       <c r="H95" t="s">
         <v>15</v>
       </c>
+      <c r="J95" t="s">
+        <v>16</v>
+      </c>
+      <c r="K95" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96">
@@ -6594,8 +6697,14 @@
       <c r="H96" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J96" t="s">
+        <v>16</v>
+      </c>
+      <c r="K96" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>1036962271</v>
       </c>
@@ -6620,8 +6729,14 @@
       <c r="H97" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J97" t="s">
+        <v>16</v>
+      </c>
+      <c r="K97" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>1036962271</v>
       </c>
@@ -6646,8 +6761,14 @@
       <c r="H98" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J98" t="s">
+        <v>16</v>
+      </c>
+      <c r="K98" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>1036962271</v>
       </c>
@@ -6672,8 +6793,14 @@
       <c r="H99" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J99" t="s">
+        <v>16</v>
+      </c>
+      <c r="K99" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>1036962271</v>
       </c>
@@ -6698,8 +6825,14 @@
       <c r="H100" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J100" t="s">
+        <v>16</v>
+      </c>
+      <c r="K100" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>1036962271</v>
       </c>
@@ -6724,8 +6857,14 @@
       <c r="H101" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J101" t="s">
+        <v>16</v>
+      </c>
+      <c r="K101" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>1036962271</v>
       </c>
@@ -6750,8 +6889,14 @@
       <c r="H102" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J102" t="s">
+        <v>16</v>
+      </c>
+      <c r="K102" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>1036962271</v>
       </c>
@@ -6776,8 +6921,14 @@
       <c r="H103" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J103" t="s">
+        <v>16</v>
+      </c>
+      <c r="K103" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>1036962271</v>
       </c>
@@ -6802,8 +6953,14 @@
       <c r="H104" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J104" t="s">
+        <v>16</v>
+      </c>
+      <c r="K104" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>1036962271</v>
       </c>
@@ -6828,8 +6985,14 @@
       <c r="H105" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J105" t="s">
+        <v>16</v>
+      </c>
+      <c r="K105" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>1036962271</v>
       </c>
@@ -6854,8 +7017,14 @@
       <c r="H106" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J106" t="s">
+        <v>16</v>
+      </c>
+      <c r="K106" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>1036962271</v>
       </c>
@@ -6880,8 +7049,14 @@
       <c r="H107" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J107" t="s">
+        <v>16</v>
+      </c>
+      <c r="K107" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>1036962271</v>
       </c>
@@ -6906,8 +7081,14 @@
       <c r="H108" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J108" t="s">
+        <v>16</v>
+      </c>
+      <c r="K108" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>1036962271</v>
       </c>
@@ -6932,8 +7113,14 @@
       <c r="H109" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J109" t="s">
+        <v>16</v>
+      </c>
+      <c r="K109" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>1036962271</v>
       </c>
@@ -6958,8 +7145,14 @@
       <c r="H110" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J110" t="s">
+        <v>16</v>
+      </c>
+      <c r="K110" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>1036962271</v>
       </c>
@@ -6984,8 +7177,14 @@
       <c r="H111" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J111" t="s">
+        <v>16</v>
+      </c>
+      <c r="K111" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>1036962271</v>
       </c>
@@ -7010,8 +7209,14 @@
       <c r="H112" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J112" t="s">
+        <v>16</v>
+      </c>
+      <c r="K112" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>1036962271</v>
       </c>
@@ -7036,8 +7241,14 @@
       <c r="H113" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J113" t="s">
+        <v>16</v>
+      </c>
+      <c r="K113" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>1036962271</v>
       </c>
@@ -7062,8 +7273,14 @@
       <c r="H114" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J114" t="s">
+        <v>16</v>
+      </c>
+      <c r="K114" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>1036962271</v>
       </c>
@@ -7088,8 +7305,14 @@
       <c r="H115" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J115" t="s">
+        <v>25</v>
+      </c>
+      <c r="K115" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>1036962271</v>
       </c>
@@ -7114,8 +7337,14 @@
       <c r="H116" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J116" t="s">
+        <v>16</v>
+      </c>
+      <c r="K116" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>1036962271</v>
       </c>
@@ -7140,8 +7369,14 @@
       <c r="H117" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J117" t="s">
+        <v>16</v>
+      </c>
+      <c r="K117" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>1036962271</v>
       </c>
@@ -7166,8 +7401,14 @@
       <c r="H118" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J118" t="s">
+        <v>16</v>
+      </c>
+      <c r="K118" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>1036962271</v>
       </c>
@@ -7192,8 +7433,14 @@
       <c r="H119" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J119" t="s">
+        <v>16</v>
+      </c>
+      <c r="K119" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>1036962271</v>
       </c>
@@ -7218,8 +7465,14 @@
       <c r="H120" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J120" t="s">
+        <v>16</v>
+      </c>
+      <c r="K120" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>1036962271</v>
       </c>
@@ -7244,8 +7497,14 @@
       <c r="H121" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J121" t="s">
+        <v>16</v>
+      </c>
+      <c r="K121" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>1036962271</v>
       </c>
@@ -7270,8 +7529,14 @@
       <c r="H122" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J122" t="s">
+        <v>16</v>
+      </c>
+      <c r="K122" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>1036962271</v>
       </c>
@@ -7296,8 +7561,14 @@
       <c r="H123" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J123" t="s">
+        <v>16</v>
+      </c>
+      <c r="K123" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>1036962271</v>
       </c>
@@ -7322,8 +7593,14 @@
       <c r="H124" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J124" t="s">
+        <v>16</v>
+      </c>
+      <c r="K124" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>1036962271</v>
       </c>
@@ -7348,8 +7625,14 @@
       <c r="H125" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J125" t="s">
+        <v>16</v>
+      </c>
+      <c r="K125" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>1036962271</v>
       </c>
@@ -7374,8 +7657,14 @@
       <c r="H126" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J126" t="s">
+        <v>16</v>
+      </c>
+      <c r="K126" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>1036962271</v>
       </c>
@@ -7400,8 +7689,14 @@
       <c r="H127" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J127" t="s">
+        <v>16</v>
+      </c>
+      <c r="K127" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>1036962271</v>
       </c>
@@ -7426,8 +7721,14 @@
       <c r="H128" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J128" t="s">
+        <v>16</v>
+      </c>
+      <c r="K128" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>1036962271</v>
       </c>
@@ -7452,8 +7753,14 @@
       <c r="H129" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J129" t="s">
+        <v>16</v>
+      </c>
+      <c r="K129" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>1036962271</v>
       </c>
@@ -7478,8 +7785,14 @@
       <c r="H130" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J130" t="s">
+        <v>16</v>
+      </c>
+      <c r="K130" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>1036962271</v>
       </c>
@@ -7504,8 +7817,14 @@
       <c r="H131" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J131" t="s">
+        <v>16</v>
+      </c>
+      <c r="K131" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>1036962271</v>
       </c>
@@ -7530,8 +7849,14 @@
       <c r="H132" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J132" t="s">
+        <v>16</v>
+      </c>
+      <c r="K132" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>1036962271</v>
       </c>
@@ -7556,8 +7881,14 @@
       <c r="H133" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J133" t="s">
+        <v>16</v>
+      </c>
+      <c r="K133" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>1036962271</v>
       </c>
@@ -7582,8 +7913,14 @@
       <c r="H134" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J134" t="s">
+        <v>16</v>
+      </c>
+      <c r="K134" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>1036962271</v>
       </c>
@@ -7608,8 +7945,14 @@
       <c r="H135" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J135" t="s">
+        <v>16</v>
+      </c>
+      <c r="K135" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>1036962271</v>
       </c>
@@ -7634,22 +7977,28 @@
       <c r="H136" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J136" t="s">
+        <v>25</v>
+      </c>
+      <c r="K136" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>1036962271</v>
       </c>
       <c r="B137" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C137" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D137">
         <v>3112964308</v>
       </c>
       <c r="E137" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F137" t="s">
         <v>108</v>
@@ -7660,25 +8009,31 @@
       <c r="H137" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J137" t="s">
+        <v>16</v>
+      </c>
+      <c r="K137" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>1036962271</v>
       </c>
       <c r="B138" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C138" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D138">
         <v>3114460310</v>
       </c>
       <c r="E138" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F138" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="G138">
         <v>1102858674</v>
@@ -7686,25 +8041,31 @@
       <c r="H138" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J138" t="s">
+        <v>16</v>
+      </c>
+      <c r="K138" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>1036962271</v>
       </c>
       <c r="B139" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C139" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D139">
         <v>3112731493</v>
       </c>
       <c r="E139" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F139" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="G139">
         <v>8292209</v>
@@ -7712,25 +8073,31 @@
       <c r="H139" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J139" t="s">
+        <v>16</v>
+      </c>
+      <c r="K139" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>1036962271</v>
       </c>
       <c r="B140" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C140" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D140">
         <v>3213766364</v>
       </c>
       <c r="E140" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F140" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G140">
         <v>63562832</v>
@@ -7738,25 +8105,31 @@
       <c r="H140" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J140" t="s">
+        <v>25</v>
+      </c>
+      <c r="K140" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>1036962271</v>
       </c>
       <c r="B141" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C141" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D141">
         <v>3112909693</v>
       </c>
       <c r="E141" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F141" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G141">
         <v>63534437</v>
@@ -7764,25 +8137,31 @@
       <c r="H141" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J141" t="s">
+        <v>16</v>
+      </c>
+      <c r="K141" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>1036962271</v>
       </c>
       <c r="B142" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C142" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D142">
         <v>3133155379</v>
       </c>
       <c r="E142" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F142" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="G142">
         <v>1072699782</v>
@@ -7790,25 +8169,31 @@
       <c r="H142" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J142" t="s">
+        <v>16</v>
+      </c>
+      <c r="K142" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>1036962271</v>
       </c>
       <c r="B143" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C143" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D143">
         <v>3213756390</v>
       </c>
       <c r="E143" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F143" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="G143">
         <v>11313216</v>
@@ -7816,25 +8201,31 @@
       <c r="H143" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J143" t="s">
+        <v>16</v>
+      </c>
+      <c r="K143" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>1036962271</v>
       </c>
       <c r="B144" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C144" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D144">
         <v>3133188094</v>
       </c>
       <c r="E144" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F144" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="G144">
         <v>37241084</v>
@@ -7842,25 +8233,31 @@
       <c r="H144" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J144" t="s">
+        <v>16</v>
+      </c>
+      <c r="K144" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>1036962271</v>
       </c>
       <c r="B145" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C145" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D145">
         <v>3203977059</v>
       </c>
       <c r="E145" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F145" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="G145">
         <v>1127620900</v>
@@ -7868,25 +8265,31 @@
       <c r="H145" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J145" t="s">
+        <v>16</v>
+      </c>
+      <c r="K145" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>1036962271</v>
       </c>
       <c r="B146" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C146" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D146">
         <v>3203965151</v>
       </c>
       <c r="E146" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F146" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="G146">
         <v>1065865230</v>
@@ -7894,25 +8297,31 @@
       <c r="H146" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J146" t="s">
+        <v>16</v>
+      </c>
+      <c r="K146" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>1036962271</v>
       </c>
       <c r="B147" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C147" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D147">
         <v>3114405685</v>
       </c>
       <c r="E147" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F147" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="G147">
         <v>1004381546</v>
@@ -7920,25 +8329,31 @@
       <c r="H147" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J147" t="s">
+        <v>16</v>
+      </c>
+      <c r="K147" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>1036962271</v>
       </c>
       <c r="B148" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C148" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D148">
         <v>3114496762</v>
       </c>
       <c r="E148" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F148" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="G148">
         <v>26670520</v>
@@ -7946,25 +8361,31 @@
       <c r="H148" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J148" t="s">
+        <v>16</v>
+      </c>
+      <c r="K148" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>1036962271</v>
       </c>
       <c r="B149" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C149" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D149">
         <v>3102420996</v>
       </c>
       <c r="E149" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F149" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="G149">
         <v>1038099458</v>
@@ -7972,22 +8393,28 @@
       <c r="H149" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J149" t="s">
+        <v>16</v>
+      </c>
+      <c r="K149" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>1036962271</v>
       </c>
       <c r="B150" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C150" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D150">
         <v>3203960507</v>
       </c>
       <c r="E150" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F150" t="s">
         <v>278</v>
@@ -7998,25 +8425,31 @@
       <c r="H150" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J150" t="s">
+        <v>16</v>
+      </c>
+      <c r="K150" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>1036962271</v>
       </c>
       <c r="B151" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C151" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D151">
         <v>3213781496</v>
       </c>
       <c r="E151" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="F151" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="G151">
         <v>1002492811</v>
@@ -8024,25 +8457,31 @@
       <c r="H151" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J151" t="s">
+        <v>16</v>
+      </c>
+      <c r="K151" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>1036962271</v>
       </c>
       <c r="B152" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C152" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D152">
         <v>3203994765</v>
       </c>
       <c r="E152" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="F152" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="G152">
         <v>1007833419</v>
@@ -8050,25 +8489,31 @@
       <c r="H152" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J152" t="s">
+        <v>16</v>
+      </c>
+      <c r="K152" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>1036962271</v>
       </c>
       <c r="B153" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C153" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D153">
         <v>3133192205</v>
       </c>
       <c r="E153" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="F153" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="G153">
         <v>4548800</v>
@@ -8076,25 +8521,31 @@
       <c r="H153" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J153" t="s">
+        <v>16</v>
+      </c>
+      <c r="K153" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>1036962271</v>
       </c>
       <c r="B154" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C154" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D154">
         <v>3213732649</v>
       </c>
       <c r="E154" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F154" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="G154">
         <v>1076321364</v>
@@ -8102,25 +8553,31 @@
       <c r="H154" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J154" t="s">
+        <v>25</v>
+      </c>
+      <c r="K154" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>1036962271</v>
       </c>
       <c r="B155" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C155" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D155">
         <v>3112952353</v>
       </c>
       <c r="E155" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F155" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G155">
         <v>79620450</v>
@@ -8128,16 +8585,22 @@
       <c r="H155" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J155" t="s">
+        <v>16</v>
+      </c>
+      <c r="K155" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>1036962271</v>
       </c>
       <c r="B156" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C156" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D156">
         <v>3112833767</v>
@@ -8146,7 +8609,7 @@
         <v>84</v>
       </c>
       <c r="F156" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="G156">
         <v>1098762544</v>
@@ -8154,25 +8617,31 @@
       <c r="H156" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J156" t="s">
+        <v>16</v>
+      </c>
+      <c r="K156" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>1036962271</v>
       </c>
       <c r="B157" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C157" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D157">
         <v>3213771494</v>
       </c>
       <c r="E157" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F157" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="G157">
         <v>72055087</v>
@@ -8180,25 +8649,31 @@
       <c r="H157" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J157" t="s">
+        <v>16</v>
+      </c>
+      <c r="K157" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>1036962271</v>
       </c>
       <c r="B158" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C158" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D158">
         <v>3203993208</v>
       </c>
       <c r="E158" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F158" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="G158">
         <v>1047334628</v>
@@ -8206,25 +8681,31 @@
       <c r="H158" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J158" t="s">
+        <v>16</v>
+      </c>
+      <c r="K158" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>1036962271</v>
       </c>
       <c r="B159" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C159" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D159">
         <v>3112881389</v>
       </c>
       <c r="E159" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F159" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="G159">
         <v>41537875</v>
@@ -8232,25 +8713,31 @@
       <c r="H159" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J159" t="s">
+        <v>25</v>
+      </c>
+      <c r="K159" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>1036962271</v>
       </c>
       <c r="B160" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C160" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D160">
         <v>3112961880</v>
       </c>
       <c r="E160" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F160" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="G160">
         <v>1015067780</v>
@@ -8258,25 +8745,31 @@
       <c r="H160" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J160" t="s">
+        <v>16</v>
+      </c>
+      <c r="K160" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>1036962271</v>
       </c>
       <c r="B161" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C161" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D161">
         <v>3133116586</v>
       </c>
       <c r="E161" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="F161" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="G161">
         <v>1049603398</v>
@@ -8284,25 +8777,31 @@
       <c r="H161" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J161" t="s">
+        <v>16</v>
+      </c>
+      <c r="K161" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>1036962271</v>
       </c>
       <c r="B162" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C162" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D162">
         <v>3209320995</v>
       </c>
       <c r="E162" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="F162" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G162">
         <v>39420003</v>
@@ -8310,25 +8809,31 @@
       <c r="H162" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J162" t="s">
+        <v>16</v>
+      </c>
+      <c r="K162" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>1036962271</v>
       </c>
       <c r="B163" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C163" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D163">
         <v>3123574149</v>
       </c>
       <c r="E163" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="F163" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="G163">
         <v>71745580</v>
@@ -8336,25 +8841,31 @@
       <c r="H163" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J163" t="s">
+        <v>16</v>
+      </c>
+      <c r="K163" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>1036962271</v>
       </c>
       <c r="B164" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C164" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D164">
         <v>3123553934</v>
       </c>
       <c r="E164" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="F164" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="G164">
         <v>71745580</v>
@@ -8362,25 +8873,31 @@
       <c r="H164" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J164" t="s">
+        <v>16</v>
+      </c>
+      <c r="K164" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>1036962271</v>
       </c>
       <c r="B165" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C165" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D165">
         <v>3123553903</v>
       </c>
       <c r="E165" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="F165" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="G165">
         <v>71745580</v>
@@ -8388,22 +8905,28 @@
       <c r="H165" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J165" t="s">
+        <v>16</v>
+      </c>
+      <c r="K165" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>1036962271</v>
       </c>
       <c r="B166" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C166" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D166">
         <v>3203539954</v>
       </c>
       <c r="E166" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F166" t="s">
         <v>108</v>
@@ -8414,25 +8937,31 @@
       <c r="H166" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J166" t="s">
+        <v>16</v>
+      </c>
+      <c r="K166" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>1036962271</v>
       </c>
       <c r="B167" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C167" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D167">
         <v>3123578282</v>
       </c>
       <c r="E167" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="F167" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="G167">
         <v>35696552</v>
@@ -8440,25 +8969,31 @@
       <c r="H167" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J167" t="s">
+        <v>16</v>
+      </c>
+      <c r="K167" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>1036962271</v>
       </c>
       <c r="B168" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C168" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D168">
         <v>3114529686</v>
       </c>
       <c r="E168" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="F168" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="G168">
         <v>60311165</v>
@@ -8466,25 +9001,31 @@
       <c r="H168" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J168" t="s">
+        <v>16</v>
+      </c>
+      <c r="K168" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>1036962271</v>
       </c>
       <c r="B169" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C169" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D169">
         <v>3112785206</v>
       </c>
       <c r="E169" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="F169" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="G169">
         <v>1104134701</v>
@@ -8492,25 +9033,31 @@
       <c r="H169" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J169" t="s">
+        <v>16</v>
+      </c>
+      <c r="K169" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>1036962271</v>
       </c>
       <c r="B170" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C170" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D170">
         <v>3138049860</v>
       </c>
       <c r="E170" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="F170" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="G170">
         <v>1118237052</v>
@@ -8518,25 +9065,31 @@
       <c r="H170" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J170" t="s">
+        <v>16</v>
+      </c>
+      <c r="K170" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>1036962271</v>
       </c>
       <c r="B171" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C171" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D171">
         <v>3114424570</v>
       </c>
       <c r="E171" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F171" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="G171">
         <v>6437488</v>
@@ -8544,22 +9097,28 @@
       <c r="H171" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J171" t="s">
+        <v>16</v>
+      </c>
+      <c r="K171" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>1036962271</v>
       </c>
       <c r="B172" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C172" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D172">
         <v>3133018532</v>
       </c>
       <c r="E172" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F172" t="s">
         <v>93</v>
@@ -8570,25 +9129,31 @@
       <c r="H172" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J172" t="s">
+        <v>16</v>
+      </c>
+      <c r="K172" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>1036962271</v>
       </c>
       <c r="B173" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C173" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D173">
         <v>3112902915</v>
       </c>
       <c r="E173" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F173" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="G173">
         <v>26427260</v>
@@ -8596,25 +9161,31 @@
       <c r="H173" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J173" t="s">
+        <v>16</v>
+      </c>
+      <c r="K173" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>1036962271</v>
       </c>
       <c r="B174" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C174" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D174">
         <v>3114583240</v>
       </c>
       <c r="E174" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F174" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="G174">
         <v>1000851959</v>
@@ -8622,25 +9193,31 @@
       <c r="H174" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J174" t="s">
+        <v>16</v>
+      </c>
+      <c r="K174" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>1036962271</v>
       </c>
       <c r="B175" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C175" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D175">
         <v>3203982035</v>
       </c>
       <c r="E175" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="F175" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="G175">
         <v>43838110</v>
@@ -8648,25 +9225,31 @@
       <c r="H175" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J175" t="s">
+        <v>16</v>
+      </c>
+      <c r="K175" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>1036962271</v>
       </c>
       <c r="B176" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C176" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D176">
         <v>3213729968</v>
       </c>
       <c r="E176" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="F176" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="G176">
         <v>1002372406</v>
@@ -8674,25 +9257,31 @@
       <c r="H176" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J176" t="s">
+        <v>16</v>
+      </c>
+      <c r="K176" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>1036962271</v>
       </c>
       <c r="B177" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C177" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D177">
         <v>3112736139</v>
       </c>
       <c r="E177" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="F177" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="G177">
         <v>98478394</v>
@@ -8700,22 +9289,28 @@
       <c r="H177" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J177" t="s">
+        <v>16</v>
+      </c>
+      <c r="K177" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>1036962271</v>
       </c>
       <c r="B178" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C178" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D178">
         <v>3143692479</v>
       </c>
       <c r="E178" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="F178" t="s">
         <v>85</v>
@@ -8726,25 +9321,31 @@
       <c r="H178" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J178" t="s">
+        <v>25</v>
+      </c>
+      <c r="K178" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>1036962271</v>
       </c>
       <c r="B179" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C179" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D179">
         <v>3208196966</v>
       </c>
       <c r="E179" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="F179" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="G179">
         <v>1037596662</v>
@@ -8752,25 +9353,31 @@
       <c r="H179" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J179" t="s">
+        <v>16</v>
+      </c>
+      <c r="K179" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>1036962271</v>
       </c>
       <c r="B180" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C180" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D180">
         <v>3203972349</v>
       </c>
       <c r="E180" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="F180" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="G180">
         <v>1086042070</v>
@@ -8778,25 +9385,31 @@
       <c r="H180" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J180" t="s">
+        <v>16</v>
+      </c>
+      <c r="K180" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>1036962271</v>
       </c>
       <c r="B181" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C181" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D181">
         <v>3213767736</v>
       </c>
       <c r="E181" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="F181" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="G181">
         <v>1070622845</v>
@@ -8804,25 +9417,31 @@
       <c r="H181" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J181" t="s">
+        <v>16</v>
+      </c>
+      <c r="K181" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>1036962271</v>
       </c>
       <c r="B182" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C182" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D182">
         <v>3213746451</v>
       </c>
       <c r="E182" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="F182" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="G182">
         <v>1077423681</v>
@@ -8830,25 +9449,31 @@
       <c r="H182" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J182" t="s">
+        <v>16</v>
+      </c>
+      <c r="K182" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>1036962271</v>
       </c>
       <c r="B183" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C183" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D183">
         <v>3112911686</v>
       </c>
       <c r="E183" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="F183" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="G183">
         <v>1034986535</v>
@@ -8856,25 +9481,31 @@
       <c r="H183" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J183" t="s">
+        <v>16</v>
+      </c>
+      <c r="K183" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>1036962271</v>
       </c>
       <c r="B184" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C184" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D184">
         <v>3214773492</v>
       </c>
       <c r="E184" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F184" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="G184">
         <v>39562136</v>
@@ -8882,25 +9513,31 @@
       <c r="H184" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J184" t="s">
+        <v>16</v>
+      </c>
+      <c r="K184" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>1036962271</v>
       </c>
       <c r="B185" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C185" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D185">
         <v>3203987266</v>
       </c>
       <c r="E185" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F185" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="G185">
         <v>1144055180</v>
@@ -8908,25 +9545,31 @@
       <c r="H185" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J185" t="s">
+        <v>16</v>
+      </c>
+      <c r="K185" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>1036962271</v>
       </c>
       <c r="B186" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C186" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D186">
         <v>3133142589</v>
       </c>
       <c r="E186" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F186" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="G186">
         <v>56103602</v>
@@ -8934,25 +9577,31 @@
       <c r="H186" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J186" t="s">
+        <v>25</v>
+      </c>
+      <c r="K186" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>1036962271</v>
       </c>
       <c r="B187" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C187" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="D187">
         <v>3133229642</v>
       </c>
       <c r="E187" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="F187" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="G187">
         <v>1125802890</v>
@@ -8960,16 +9609,22 @@
       <c r="H187" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J187" t="s">
+        <v>25</v>
+      </c>
+      <c r="K187" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>1036962271</v>
       </c>
       <c r="B188" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C188" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="D188">
         <v>3114456753</v>
@@ -8978,7 +9633,7 @@
         <v>369</v>
       </c>
       <c r="F188" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="G188">
         <v>31954910</v>
@@ -8986,25 +9641,31 @@
       <c r="H188" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J188" t="s">
+        <v>25</v>
+      </c>
+      <c r="K188" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>1036962271</v>
       </c>
       <c r="B189" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C189" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="D189">
         <v>3213743791</v>
       </c>
       <c r="E189" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="F189" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="G189">
         <v>1010107176</v>
@@ -9012,25 +9673,31 @@
       <c r="H189" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J189" t="s">
+        <v>16</v>
+      </c>
+      <c r="K189" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>1036962271</v>
       </c>
       <c r="B190" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C190" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="D190">
         <v>3114738021</v>
       </c>
       <c r="E190" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="F190" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="G190">
         <v>1018469972</v>
@@ -9038,25 +9705,31 @@
       <c r="H190" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J190" t="s">
+        <v>16</v>
+      </c>
+      <c r="K190" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>1036962271</v>
       </c>
       <c r="B191" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C191" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="D191">
         <v>3112949764</v>
       </c>
       <c r="E191" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F191" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="G191">
         <v>1095912998</v>
@@ -9064,25 +9737,31 @@
       <c r="H191" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J191" t="s">
+        <v>16</v>
+      </c>
+      <c r="K191" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>1036962271</v>
       </c>
       <c r="B192" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C192" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D192">
         <v>3114712981</v>
       </c>
       <c r="E192" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="F192" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G192">
         <v>1025525046</v>
@@ -9090,25 +9769,31 @@
       <c r="H192" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J192" t="s">
+        <v>16</v>
+      </c>
+      <c r="K192" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>1036962271</v>
       </c>
       <c r="B193" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C193" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="D193">
         <v>3203975654</v>
       </c>
       <c r="E193" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="F193" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="G193">
         <v>43004342</v>
@@ -9116,25 +9801,31 @@
       <c r="H193" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J193" t="s">
+        <v>16</v>
+      </c>
+      <c r="K193" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>1036962271</v>
       </c>
       <c r="B194" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C194" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="D194">
         <v>3114671568</v>
       </c>
       <c r="E194" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="F194" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="G194">
         <v>4275707</v>
@@ -9142,25 +9833,31 @@
       <c r="H194" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J194" t="s">
+        <v>16</v>
+      </c>
+      <c r="K194" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>1036962271</v>
       </c>
       <c r="B195" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C195" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="D195">
         <v>3133249632</v>
       </c>
       <c r="E195" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="F195" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="G195">
         <v>1007703733</v>
@@ -9168,22 +9865,28 @@
       <c r="H195" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J195" t="s">
+        <v>16</v>
+      </c>
+      <c r="K195" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>1036962271</v>
       </c>
       <c r="B196" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C196" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="D196">
         <v>3112910218</v>
       </c>
       <c r="E196" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="F196" t="s">
         <v>300</v>
@@ -9194,25 +9897,31 @@
       <c r="H196" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J196" t="s">
+        <v>16</v>
+      </c>
+      <c r="K196" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>1036962271</v>
       </c>
       <c r="B197" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C197" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="D197">
         <v>3203998101</v>
       </c>
       <c r="E197" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="F197" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="G197">
         <v>80755990</v>
@@ -9220,25 +9929,31 @@
       <c r="H197" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J197" t="s">
+        <v>16</v>
+      </c>
+      <c r="K197" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>1036962271</v>
       </c>
       <c r="B198" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C198" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="D198">
         <v>3203980705</v>
       </c>
       <c r="E198" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="F198" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="G198">
         <v>98673739</v>
@@ -9246,25 +9961,31 @@
       <c r="H198" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J198" t="s">
+        <v>16</v>
+      </c>
+      <c r="K198" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>1036962271</v>
       </c>
       <c r="B199" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="C199" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="D199">
         <v>3114645300</v>
       </c>
       <c r="E199" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="F199" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="G199">
         <v>9272355</v>
@@ -9272,25 +9993,31 @@
       <c r="H199" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J199" t="s">
+        <v>16</v>
+      </c>
+      <c r="K199" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>1036962271</v>
       </c>
       <c r="B200" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C200" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="D200">
         <v>3133230821</v>
       </c>
       <c r="E200" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="F200" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="G200">
         <v>80418645</v>
@@ -9298,25 +10025,31 @@
       <c r="H200" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J200" t="s">
+        <v>16</v>
+      </c>
+      <c r="K200" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>1036962271</v>
       </c>
       <c r="B201" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="C201" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="D201">
         <v>3213726180</v>
       </c>
       <c r="E201" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="F201" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="G201">
         <v>1007956938</v>
@@ -9324,25 +10057,31 @@
       <c r="H201" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J201" t="s">
+        <v>16</v>
+      </c>
+      <c r="K201" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>1036962271</v>
       </c>
       <c r="B202" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="C202" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="D202">
         <v>3138096036</v>
       </c>
       <c r="E202" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="F202" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="G202">
         <v>1050094140</v>
@@ -9350,25 +10089,31 @@
       <c r="H202" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J202" t="s">
+        <v>16</v>
+      </c>
+      <c r="K202" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>1036962271</v>
       </c>
       <c r="B203" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="C203" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="D203">
         <v>3114714665</v>
       </c>
       <c r="E203" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="F203" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="G203">
         <v>45525938</v>
@@ -9376,22 +10121,28 @@
       <c r="H203" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J203" t="s">
+        <v>16</v>
+      </c>
+      <c r="K203" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>1036962271</v>
       </c>
       <c r="B204" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C204" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="D204">
         <v>3203964487</v>
       </c>
       <c r="E204" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="F204" t="s">
         <v>221</v>
@@ -9402,25 +10153,31 @@
       <c r="H204" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J204" t="s">
+        <v>16</v>
+      </c>
+      <c r="K204" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>1036962271</v>
       </c>
       <c r="B205" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="C205" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="D205">
         <v>3112837747</v>
       </c>
       <c r="E205" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="F205" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="G205">
         <v>1002937212</v>
@@ -9428,25 +10185,31 @@
       <c r="H205" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J205" t="s">
+        <v>16</v>
+      </c>
+      <c r="K205" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>1036962271</v>
       </c>
       <c r="B206" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="C206" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="D206">
         <v>3203963291</v>
       </c>
       <c r="E206" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="F206" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="G206">
         <v>22456858</v>
@@ -9454,25 +10217,31 @@
       <c r="H206" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J206" t="s">
+        <v>16</v>
+      </c>
+      <c r="K206" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>1036962271</v>
       </c>
       <c r="B207" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="C207" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="D207">
         <v>3114695409</v>
       </c>
       <c r="E207" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="F207" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="G207">
         <v>1098827363</v>
@@ -9480,22 +10249,28 @@
       <c r="H207" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J207" t="s">
+        <v>16</v>
+      </c>
+      <c r="K207" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>1036962271</v>
       </c>
       <c r="B208" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="C208" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="D208">
         <v>3213779131</v>
       </c>
       <c r="E208" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="F208" t="s">
         <v>89</v>
@@ -9506,25 +10281,31 @@
       <c r="H208" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J208" t="s">
+        <v>16</v>
+      </c>
+      <c r="K208" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>1036962271</v>
       </c>
       <c r="B209" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="C209" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="D209">
         <v>3203961546</v>
       </c>
       <c r="E209" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="F209" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="G209">
         <v>1052959170</v>
@@ -9532,25 +10313,31 @@
       <c r="H209" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J209" t="s">
+        <v>16</v>
+      </c>
+      <c r="K209" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>1036962271</v>
       </c>
       <c r="B210" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="C210" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="D210">
         <v>3114458048</v>
       </c>
       <c r="E210" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="F210" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G210">
         <v>1067879534</v>
@@ -9558,25 +10345,31 @@
       <c r="H210" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J210" t="s">
+        <v>16</v>
+      </c>
+      <c r="K210" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>1036962271</v>
       </c>
       <c r="B211" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C211" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="D211">
         <v>3114694620</v>
       </c>
       <c r="E211" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="F211" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="G211">
         <v>1000063697</v>
@@ -9584,25 +10377,31 @@
       <c r="H211" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J211" t="s">
+        <v>25</v>
+      </c>
+      <c r="K211" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>1036962271</v>
       </c>
       <c r="B212" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C212" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="D212">
         <v>3114660930</v>
       </c>
       <c r="E212" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="F212" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="G212">
         <v>1059234523</v>
@@ -9610,22 +10409,28 @@
       <c r="H212" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J212" t="s">
+        <v>16</v>
+      </c>
+      <c r="K212" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>1036962271</v>
       </c>
       <c r="B213" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="C213" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="D213">
         <v>3138092253</v>
       </c>
       <c r="E213" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="F213" t="s">
         <v>112</v>
@@ -9636,25 +10441,31 @@
       <c r="H213" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J213" t="s">
+        <v>16</v>
+      </c>
+      <c r="K213" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>1036962271</v>
       </c>
       <c r="B214" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="C214" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="D214">
         <v>3114685495</v>
       </c>
       <c r="E214" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="F214" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="G214">
         <v>1017237837</v>
@@ -9662,25 +10473,31 @@
       <c r="H214" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J214" t="s">
+        <v>16</v>
+      </c>
+      <c r="K214" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>1036962271</v>
       </c>
       <c r="B215" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="C215" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="D215">
         <v>3112744503</v>
       </c>
       <c r="E215" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="F215" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="G215">
         <v>1003190345</v>
@@ -9688,25 +10505,31 @@
       <c r="H215" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J215" t="s">
+        <v>16</v>
+      </c>
+      <c r="K215" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>1036962271</v>
       </c>
       <c r="B216" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="C216" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D216">
         <v>3114719792</v>
       </c>
       <c r="E216" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="F216" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="G216">
         <v>1107507509</v>
@@ -9714,25 +10537,31 @@
       <c r="H216" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J216" t="s">
+        <v>25</v>
+      </c>
+      <c r="K216" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>1036962271</v>
       </c>
       <c r="B217" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="C217" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="D217">
         <v>3114732101</v>
       </c>
       <c r="E217" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="F217" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="G217">
         <v>1032441481</v>
@@ -9740,25 +10569,31 @@
       <c r="H217" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J217" t="s">
+        <v>16</v>
+      </c>
+      <c r="K217" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>1036962271</v>
       </c>
       <c r="B218" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C218" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="D218">
         <v>3138078303</v>
       </c>
       <c r="E218" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="F218" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="G218">
         <v>1012317887</v>
@@ -9766,25 +10601,31 @@
       <c r="H218" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J218" t="s">
+        <v>16</v>
+      </c>
+      <c r="K218" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>1036962271</v>
       </c>
       <c r="B219" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C219" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="D219">
         <v>3214797547</v>
       </c>
       <c r="E219" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="F219" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="G219">
         <v>66758090</v>
@@ -9792,25 +10633,31 @@
       <c r="H219" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J219" t="s">
+        <v>16</v>
+      </c>
+      <c r="K219" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>1036962271</v>
       </c>
       <c r="B220" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="C220" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="D220">
         <v>3132975023</v>
       </c>
       <c r="E220" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="F220" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="G220">
         <v>51907024</v>
@@ -9818,25 +10665,31 @@
       <c r="H220" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J220" t="s">
+        <v>16</v>
+      </c>
+      <c r="K220" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>1036962271</v>
       </c>
       <c r="B221" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="C221" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="D221">
         <v>3203542474</v>
       </c>
       <c r="E221" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="F221" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="G221">
         <v>1038119844</v>
@@ -9844,25 +10697,31 @@
       <c r="H221" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J221" t="s">
+        <v>16</v>
+      </c>
+      <c r="K221" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>1036962271</v>
       </c>
       <c r="B222" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="C222" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="D222">
         <v>3212978285</v>
       </c>
       <c r="E222" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="F222" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="G222">
         <v>29351054</v>
@@ -9870,25 +10729,31 @@
       <c r="H222" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J222" t="s">
+        <v>16</v>
+      </c>
+      <c r="K222" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>1036962271</v>
       </c>
       <c r="B223" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="C223" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="D223">
         <v>3114685326</v>
       </c>
       <c r="E223" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="F223" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="G223">
         <v>31320344</v>
@@ -9896,25 +10761,31 @@
       <c r="H223" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J223" t="s">
+        <v>16</v>
+      </c>
+      <c r="K223" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>1036962271</v>
       </c>
       <c r="B224" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="C224" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="D224">
         <v>3132979395</v>
       </c>
       <c r="E224" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="F224" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="G224">
         <v>14234343</v>
@@ -9922,25 +10793,31 @@
       <c r="H224" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J224" t="s">
+        <v>16</v>
+      </c>
+      <c r="K224" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>1036962271</v>
       </c>
       <c r="B225" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="C225" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="D225">
         <v>3203982062</v>
       </c>
       <c r="E225" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="F225" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="G225">
         <v>1016059369</v>
@@ -9948,25 +10825,31 @@
       <c r="H225" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J225" t="s">
+        <v>16</v>
+      </c>
+      <c r="K225" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>1036962271</v>
       </c>
       <c r="B226" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C226" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D226">
         <v>3114648345</v>
       </c>
       <c r="E226" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="F226" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="G226">
         <v>1006820766</v>
@@ -9974,25 +10857,31 @@
       <c r="H226" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J226" t="s">
+        <v>16</v>
+      </c>
+      <c r="K226" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>1036962271</v>
       </c>
       <c r="B227" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="C227" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="D227">
         <v>3112903378</v>
       </c>
       <c r="E227" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="F227" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="G227">
         <v>33816312</v>
@@ -10000,25 +10889,31 @@
       <c r="H227" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J227" t="s">
+        <v>16</v>
+      </c>
+      <c r="K227" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>1036962271</v>
       </c>
       <c r="B228" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="C228" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="D228">
         <v>3133146842</v>
       </c>
       <c r="E228" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="F228" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="G228">
         <v>1030635726</v>
@@ -10026,25 +10921,31 @@
       <c r="H228" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J228" t="s">
+        <v>16</v>
+      </c>
+      <c r="K228" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>1036962271</v>
       </c>
       <c r="B229" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C229" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="D229">
         <v>3114503600</v>
       </c>
       <c r="E229" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="F229" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="G229">
         <v>1083553701</v>
@@ -10052,25 +10953,31 @@
       <c r="H229" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J229" t="s">
+        <v>16</v>
+      </c>
+      <c r="K229" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>1036962271</v>
       </c>
       <c r="B230" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="C230" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="D230">
         <v>3114661515</v>
       </c>
       <c r="E230" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="F230" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="G230">
         <v>1221971143</v>
@@ -10078,25 +10985,31 @@
       <c r="H230" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J230" t="s">
+        <v>16</v>
+      </c>
+      <c r="K230" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>1036962271</v>
       </c>
       <c r="B231" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="C231" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="D231">
         <v>3203984158</v>
       </c>
       <c r="E231" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="F231" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="G231">
         <v>1019087414</v>
@@ -10104,25 +11017,31 @@
       <c r="H231" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J231" t="s">
+        <v>16</v>
+      </c>
+      <c r="K231" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>1036962271</v>
       </c>
       <c r="B232" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C232" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="D232">
         <v>3213788795</v>
       </c>
       <c r="E232" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="F232" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="G232">
         <v>1003510788</v>
@@ -10130,25 +11049,31 @@
       <c r="H232" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J232" t="s">
+        <v>16</v>
+      </c>
+      <c r="K232" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>1036962271</v>
       </c>
       <c r="B233" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="C233" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="D233">
         <v>3222825628</v>
       </c>
       <c r="E233" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F233" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="G233">
         <v>14569574</v>
@@ -10156,25 +11081,31 @@
       <c r="H233" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J233" t="s">
+        <v>16</v>
+      </c>
+      <c r="K233" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>1036962271</v>
       </c>
       <c r="B234" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C234" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="D234">
         <v>3203960387</v>
       </c>
       <c r="E234" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="F234" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="G234">
         <v>1006291802</v>
@@ -10182,25 +11113,31 @@
       <c r="H234" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J234" t="s">
+        <v>16</v>
+      </c>
+      <c r="K234" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>1036962271</v>
       </c>
       <c r="B235" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C235" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="D235">
         <v>3203994231</v>
       </c>
       <c r="E235" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="F235" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="G235">
         <v>1098633181</v>
@@ -10208,25 +11145,31 @@
       <c r="H235" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J235" t="s">
+        <v>16</v>
+      </c>
+      <c r="K235" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>1036962271</v>
       </c>
       <c r="B236" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="C236" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="D236">
         <v>3114663254</v>
       </c>
       <c r="E236" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="F236" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="G236">
         <v>88177243</v>
@@ -10234,22 +11177,28 @@
       <c r="H236" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J236" t="s">
+        <v>16</v>
+      </c>
+      <c r="K236" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>1036962271</v>
       </c>
       <c r="B237" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="C237" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="D237">
         <v>3112873492</v>
       </c>
       <c r="E237" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="F237" t="s">
         <v>481</v>
@@ -10260,25 +11209,31 @@
       <c r="H237" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J237" t="s">
+        <v>25</v>
+      </c>
+      <c r="K237" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>1036962271</v>
       </c>
       <c r="B238" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="C238" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="D238">
         <v>3213731293</v>
       </c>
       <c r="E238" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="F238" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="G238">
         <v>1006095484</v>
@@ -10286,25 +11241,31 @@
       <c r="H238" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J238" t="s">
+        <v>16</v>
+      </c>
+      <c r="K238" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>1036962271</v>
       </c>
       <c r="B239" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="C239" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="D239">
         <v>3114637280</v>
       </c>
       <c r="E239" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="F239" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G239">
         <v>51614666</v>
@@ -10312,25 +11273,31 @@
       <c r="H239" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J239" t="s">
+        <v>16</v>
+      </c>
+      <c r="K239" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>1036962271</v>
       </c>
       <c r="B240" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C240" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="D240">
         <v>3136408536</v>
       </c>
       <c r="E240" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="F240" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="G240">
         <v>75084675</v>
@@ -10338,25 +11305,31 @@
       <c r="H240" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J240" t="s">
+        <v>16</v>
+      </c>
+      <c r="K240" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>1036962271</v>
       </c>
       <c r="B241" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="C241" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="D241">
         <v>3208250176</v>
       </c>
       <c r="E241" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="F241" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="G241">
         <v>1140876336</v>
@@ -10364,25 +11337,31 @@
       <c r="H241" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J241" t="s">
+        <v>25</v>
+      </c>
+      <c r="K241" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="242" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>1036962271</v>
       </c>
       <c r="B242" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="C242" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="D242">
         <v>3112814110</v>
       </c>
       <c r="E242" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="F242" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="G242">
         <v>39616101</v>
@@ -10390,25 +11369,31 @@
       <c r="H242" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J242" t="s">
+        <v>16</v>
+      </c>
+      <c r="K242" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="243" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>1036962271</v>
       </c>
       <c r="B243" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="C243" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="D243">
         <v>3114719559</v>
       </c>
       <c r="E243" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="F243" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="G243">
         <v>1015462537</v>
@@ -10416,25 +11401,31 @@
       <c r="H243" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J243" t="s">
+        <v>16</v>
+      </c>
+      <c r="K243" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="244" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>1036962271</v>
       </c>
       <c r="B244" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C244" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="D244">
         <v>3112864424</v>
       </c>
       <c r="E244" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="F244" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="G244">
         <v>6248815</v>
@@ -10442,25 +11433,31 @@
       <c r="H244" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J244" t="s">
+        <v>16</v>
+      </c>
+      <c r="K244" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="245" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>1036962271</v>
       </c>
       <c r="B245" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="C245" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="D245">
         <v>3133230201</v>
       </c>
       <c r="E245" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="F245" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="G245">
         <v>52379482</v>
@@ -10468,25 +11465,31 @@
       <c r="H245" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J245" t="s">
+        <v>16</v>
+      </c>
+      <c r="K245" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="246" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>1036962271</v>
       </c>
       <c r="B246" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="C246" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="D246">
         <v>3203992387</v>
       </c>
       <c r="E246" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="F246" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="G246">
         <v>28213494</v>
@@ -10494,25 +11497,31 @@
       <c r="H246" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J246" t="s">
+        <v>16</v>
+      </c>
+      <c r="K246" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="247" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>1036962271</v>
       </c>
       <c r="B247" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="C247" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="D247">
         <v>3133011249</v>
       </c>
       <c r="E247" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="F247" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="G247">
         <v>1010022279</v>
@@ -10520,25 +11529,31 @@
       <c r="H247" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J247" t="s">
+        <v>16</v>
+      </c>
+      <c r="K247" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="248" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>1036962271</v>
       </c>
       <c r="B248" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="C248" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="D248">
         <v>3213793465</v>
       </c>
       <c r="E248" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="F248" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="G248">
         <v>39672878</v>
@@ -10546,25 +11561,31 @@
       <c r="H248" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J248" t="s">
+        <v>16</v>
+      </c>
+      <c r="K248" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="249" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>1036962271</v>
       </c>
       <c r="B249" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="C249" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="D249">
         <v>3133174088</v>
       </c>
       <c r="E249" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="F249" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="G249">
         <v>1234791597</v>
@@ -10572,25 +11593,31 @@
       <c r="H249" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J249" t="s">
+        <v>16</v>
+      </c>
+      <c r="K249" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="250" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>1036962271</v>
       </c>
       <c r="B250" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="C250" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="D250">
         <v>3203986068</v>
       </c>
       <c r="E250" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="F250" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="G250">
         <v>1090176961</v>
@@ -10598,25 +11625,31 @@
       <c r="H250" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J250" t="s">
+        <v>16</v>
+      </c>
+      <c r="K250" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="251" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>1036962271</v>
       </c>
       <c r="B251" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C251" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D251">
         <v>3133192615</v>
       </c>
       <c r="E251" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="F251" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="G251">
         <v>1045746510</v>
@@ -10624,25 +11657,31 @@
       <c r="H251" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J251" t="s">
+        <v>16</v>
+      </c>
+      <c r="K251" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="252" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>1036962271</v>
       </c>
       <c r="B252" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="C252" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="D252">
         <v>3114481567</v>
       </c>
       <c r="E252" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="F252" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="G252">
         <v>1007305721</v>
@@ -10650,25 +11689,31 @@
       <c r="H252" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J252" t="s">
+        <v>16</v>
+      </c>
+      <c r="K252" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="253" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>1036962271</v>
       </c>
       <c r="B253" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="C253" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="D253">
         <v>3112812539</v>
       </c>
       <c r="E253" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="F253" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="G253">
         <v>23360160</v>
@@ -10676,25 +11721,31 @@
       <c r="H253" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J253" t="s">
+        <v>16</v>
+      </c>
+      <c r="K253" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="254" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>1036962271</v>
       </c>
       <c r="B254" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="C254" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="D254">
         <v>3114737834</v>
       </c>
       <c r="E254" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="F254" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="G254">
         <v>1221977404</v>
@@ -10702,25 +11753,31 @@
       <c r="H254" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J254" t="s">
+        <v>16</v>
+      </c>
+      <c r="K254" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="255" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>1036962271</v>
       </c>
       <c r="B255" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C255" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="D255">
         <v>3112960089</v>
       </c>
       <c r="E255" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="F255" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="G255">
         <v>41914834</v>
@@ -10728,25 +11785,31 @@
       <c r="H255" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J255" t="s">
+        <v>16</v>
+      </c>
+      <c r="K255" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="256" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>1036962271</v>
       </c>
       <c r="B256" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="C256" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="D256">
         <v>3112950474</v>
       </c>
       <c r="E256" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="F256" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="G256">
         <v>35418436</v>
@@ -10754,25 +11817,31 @@
       <c r="H256" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J256" t="s">
+        <v>16</v>
+      </c>
+      <c r="K256" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="257" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>1036962271</v>
       </c>
       <c r="B257" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="C257" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="D257">
         <v>3203971936</v>
       </c>
       <c r="E257" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="F257" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="G257">
         <v>1012389952</v>
@@ -10780,25 +11849,31 @@
       <c r="H257" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J257" t="s">
+        <v>16</v>
+      </c>
+      <c r="K257" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="258" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>1036962271</v>
       </c>
       <c r="B258" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="C258" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="D258">
         <v>3203964649</v>
       </c>
       <c r="E258" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="F258" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="G258">
         <v>42154217</v>
@@ -10806,25 +11881,31 @@
       <c r="H258" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J258" t="s">
+        <v>16</v>
+      </c>
+      <c r="K258" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="259" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>1036962271</v>
       </c>
       <c r="B259" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="C259" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="D259">
         <v>3213751200</v>
       </c>
       <c r="E259" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="F259" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="G259">
         <v>1047038755</v>
@@ -10832,25 +11913,31 @@
       <c r="H259" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J259" t="s">
+        <v>16</v>
+      </c>
+      <c r="K259" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="260" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>1036962271</v>
       </c>
       <c r="B260" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="C260" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="D260">
         <v>3133109075</v>
       </c>
       <c r="E260" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="F260" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="G260">
         <v>1035435207</v>
@@ -10858,25 +11945,31 @@
       <c r="H260" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J260" t="s">
+        <v>16</v>
+      </c>
+      <c r="K260" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="261" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>1036962271</v>
       </c>
       <c r="B261" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="C261" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="D261">
         <v>3213776413</v>
       </c>
       <c r="E261" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="F261" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="G261">
         <v>36505510</v>
@@ -10884,25 +11977,31 @@
       <c r="H261" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J261" t="s">
+        <v>16</v>
+      </c>
+      <c r="K261" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="262" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>1036962271</v>
       </c>
       <c r="B262" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="C262" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="D262">
         <v>3214815756</v>
       </c>
       <c r="E262" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="F262" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="G262">
         <v>1031123894</v>
@@ -10910,25 +12009,31 @@
       <c r="H262" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J262" t="s">
+        <v>16</v>
+      </c>
+      <c r="K262" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="263" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>1036962271</v>
       </c>
       <c r="B263" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="C263" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="D263">
         <v>3138079400</v>
       </c>
       <c r="E263" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="F263" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="G263">
         <v>19261218</v>
@@ -10936,25 +12041,31 @@
       <c r="H263" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J263" t="s">
+        <v>16</v>
+      </c>
+      <c r="K263" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="264" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>1036962271</v>
       </c>
       <c r="B264" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="C264" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="D264">
         <v>3114584818</v>
       </c>
       <c r="E264" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="F264" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="G264">
         <v>1010045751</v>
@@ -10962,22 +12073,28 @@
       <c r="H264" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J264" t="s">
+        <v>16</v>
+      </c>
+      <c r="K264" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="265" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>1036962271</v>
       </c>
       <c r="B265" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="C265" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="D265">
         <v>3214702135</v>
       </c>
       <c r="E265" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="F265" t="s">
         <v>317</v>
@@ -10988,25 +12105,31 @@
       <c r="H265" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J265" t="s">
+        <v>16</v>
+      </c>
+      <c r="K265" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="266" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>1036962271</v>
       </c>
       <c r="B266" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="C266" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="D266">
         <v>3202170284</v>
       </c>
       <c r="E266" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="F266" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="G266">
         <v>80020167</v>
@@ -11014,25 +12137,31 @@
       <c r="H266" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J266" t="s">
+        <v>16</v>
+      </c>
+      <c r="K266" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="267" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>1036962271</v>
       </c>
       <c r="B267" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="C267" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="D267">
         <v>3112797911</v>
       </c>
       <c r="E267" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="F267" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="G267">
         <v>1046399742</v>
@@ -11040,25 +12169,31 @@
       <c r="H267" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J267" t="s">
+        <v>16</v>
+      </c>
+      <c r="K267" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="268" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>1036962271</v>
       </c>
       <c r="B268" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="C268" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="D268">
         <v>3133106253</v>
       </c>
       <c r="E268" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="F268" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="G268">
         <v>1235246210</v>
@@ -11066,25 +12201,31 @@
       <c r="H268" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J268" t="s">
+        <v>16</v>
+      </c>
+      <c r="K268" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="269" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>1036962271</v>
       </c>
       <c r="B269" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="C269" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="D269">
         <v>3133223519</v>
       </c>
       <c r="E269" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="F269" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="G269">
         <v>1092340282</v>
@@ -11092,25 +12233,31 @@
       <c r="H269" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J269" t="s">
+        <v>16</v>
+      </c>
+      <c r="K269" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="270" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>1036962271</v>
       </c>
       <c r="B270" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="C270" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="D270">
         <v>3212936824</v>
       </c>
       <c r="E270" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="F270" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="G270">
         <v>1015405342</v>
@@ -11118,25 +12265,31 @@
       <c r="H270" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J270" t="s">
+        <v>16</v>
+      </c>
+      <c r="K270" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="271" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>1036962271</v>
       </c>
       <c r="B271" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="C271" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="D271">
         <v>3112924743</v>
       </c>
       <c r="E271" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="F271" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="G271">
         <v>1014274751</v>
@@ -11144,25 +12297,31 @@
       <c r="H271" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J271" t="s">
+        <v>25</v>
+      </c>
+      <c r="K271" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="272" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>1036962271</v>
       </c>
       <c r="B272" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="C272" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="D272">
         <v>3213724989</v>
       </c>
       <c r="E272" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="F272" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="G272">
         <v>4286913</v>
@@ -11170,25 +12329,31 @@
       <c r="H272" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J272" t="s">
+        <v>16</v>
+      </c>
+      <c r="K272" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="273" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>1036962271</v>
       </c>
       <c r="B273" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="C273" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="D273">
         <v>3213770307</v>
       </c>
       <c r="E273" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="F273" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="G273">
         <v>72220605</v>
@@ -11196,25 +12361,31 @@
       <c r="H273" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J273" t="s">
+        <v>16</v>
+      </c>
+      <c r="K273" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="274" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>1036962271</v>
       </c>
       <c r="B274" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="C274" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="D274">
         <v>3203985485</v>
       </c>
       <c r="E274" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="F274" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="G274">
         <v>8260393</v>
@@ -11222,25 +12393,31 @@
       <c r="H274" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J274" t="s">
+        <v>16</v>
+      </c>
+      <c r="K274" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="275" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>1036962271</v>
       </c>
       <c r="B275" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="C275" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="D275">
         <v>3203963852</v>
       </c>
       <c r="E275" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="F275" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="G275">
         <v>31473233</v>
@@ -11248,25 +12425,31 @@
       <c r="H275" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J275" t="s">
+        <v>16</v>
+      </c>
+      <c r="K275" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="276" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>1036962271</v>
       </c>
       <c r="B276" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="C276" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="D276">
         <v>3112492860</v>
       </c>
       <c r="E276" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="F276" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="G276">
         <v>1088304774</v>
@@ -11274,25 +12457,31 @@
       <c r="H276" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J276" t="s">
+        <v>16</v>
+      </c>
+      <c r="K276" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="277" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>1036962271</v>
       </c>
       <c r="B277" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="C277" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="D277">
         <v>3133107870</v>
       </c>
       <c r="E277" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="F277" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="G277">
         <v>79308017</v>
@@ -11300,25 +12489,31 @@
       <c r="H277" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J277" t="s">
+        <v>16</v>
+      </c>
+      <c r="K277" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="278" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>1036962271</v>
       </c>
       <c r="B278" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="C278" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="D278">
         <v>3138018163</v>
       </c>
       <c r="E278" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="F278" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="G278">
         <v>40392484</v>
@@ -11326,25 +12521,31 @@
       <c r="H278" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J278" t="s">
+        <v>16</v>
+      </c>
+      <c r="K278" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="279" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>1036962271</v>
       </c>
       <c r="B279" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="C279" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="D279">
         <v>3213758851</v>
       </c>
       <c r="E279" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="F279" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="G279">
         <v>28558196</v>
@@ -11352,25 +12553,31 @@
       <c r="H279" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J279" t="s">
+        <v>16</v>
+      </c>
+      <c r="K279" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="280" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>1036962271</v>
       </c>
       <c r="B280" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="C280" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="D280">
         <v>3114733680</v>
       </c>
       <c r="E280" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="F280" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="G280">
         <v>16510749</v>
@@ -11378,25 +12585,31 @@
       <c r="H280" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J280" t="s">
+        <v>16</v>
+      </c>
+      <c r="K280" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="281" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>1036962271</v>
       </c>
       <c r="B281" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="C281" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="D281">
         <v>3114166579</v>
       </c>
       <c r="E281" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="F281" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="G281">
         <v>1113311386</v>
@@ -11404,22 +12617,28 @@
       <c r="H281" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J281" t="s">
+        <v>16</v>
+      </c>
+      <c r="K281" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="282" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>1036962271</v>
       </c>
       <c r="B282" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="C282" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="D282">
         <v>3112904915</v>
       </c>
       <c r="E282" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F282" t="s">
         <v>112</v>
@@ -11430,25 +12649,31 @@
       <c r="H282" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J282" t="s">
+        <v>16</v>
+      </c>
+      <c r="K282" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="283" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>1036962271</v>
       </c>
       <c r="B283" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="C283" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="D283">
         <v>3114508733</v>
       </c>
       <c r="E283" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="F283" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="G283">
         <v>53093779</v>
@@ -11456,25 +12681,31 @@
       <c r="H283" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J283" t="s">
+        <v>16</v>
+      </c>
+      <c r="K283" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="284" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>1036962271</v>
       </c>
       <c r="B284" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="C284" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="D284">
         <v>3114684287</v>
       </c>
       <c r="E284" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="F284" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="G284">
         <v>1152210650</v>
@@ -11482,25 +12713,31 @@
       <c r="H284" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J284" t="s">
+        <v>16</v>
+      </c>
+      <c r="K284" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="285" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>1036962271</v>
       </c>
       <c r="B285" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="C285" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="D285">
         <v>3209310874</v>
       </c>
       <c r="E285" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="F285" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="G285">
         <v>1027945518</v>
@@ -11508,25 +12745,31 @@
       <c r="H285" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J285" t="s">
+        <v>25</v>
+      </c>
+      <c r="K285" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="286" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>1036962271</v>
       </c>
       <c r="B286" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="C286" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="D286">
         <v>3112809826</v>
       </c>
       <c r="E286" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="F286" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="G286">
         <v>84088089</v>
@@ -11534,25 +12777,31 @@
       <c r="H286" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J286" t="s">
+        <v>16</v>
+      </c>
+      <c r="K286" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="287" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>1036962271</v>
       </c>
       <c r="B287" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="C287" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="D287">
         <v>3112247621</v>
       </c>
       <c r="E287" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="F287" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="G287">
         <v>46452331</v>
@@ -11560,25 +12809,31 @@
       <c r="H287" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J287" t="s">
+        <v>16</v>
+      </c>
+      <c r="K287" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="288" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>1036962271</v>
       </c>
       <c r="B288" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="C288" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="D288">
         <v>3133132289</v>
       </c>
       <c r="E288" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="F288" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="G288">
         <v>1038548797</v>
@@ -11586,25 +12841,31 @@
       <c r="H288" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J288" t="s">
+        <v>16</v>
+      </c>
+      <c r="K288" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="289" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>1036962271</v>
       </c>
       <c r="B289" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="C289" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="D289">
         <v>3203987393</v>
       </c>
       <c r="E289" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="F289" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="G289">
         <v>1108558674</v>
@@ -11612,25 +12873,31 @@
       <c r="H289" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J289" t="s">
+        <v>16</v>
+      </c>
+      <c r="K289" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="290" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>1036962271</v>
       </c>
       <c r="B290" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="C290" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="D290">
         <v>3114640377</v>
       </c>
       <c r="E290" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="F290" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="G290">
         <v>1000203614</v>
@@ -11638,25 +12905,31 @@
       <c r="H290" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J290" t="s">
+        <v>16</v>
+      </c>
+      <c r="K290" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="291" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>1036962271</v>
       </c>
       <c r="B291" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="C291" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="D291">
         <v>3114708210</v>
       </c>
       <c r="E291" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="F291" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="G291">
         <v>1032254181</v>
@@ -11664,25 +12937,31 @@
       <c r="H291" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J291" t="s">
+        <v>16</v>
+      </c>
+      <c r="K291" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="292" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>1036962271</v>
       </c>
       <c r="B292" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="C292" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="D292">
         <v>3114652125</v>
       </c>
       <c r="E292" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="F292" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="G292">
         <v>1018492016</v>
@@ -11690,31 +12969,43 @@
       <c r="H292" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J292" t="s">
+        <v>16</v>
+      </c>
+      <c r="K292" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="293" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>1036962271</v>
       </c>
       <c r="B293" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="C293" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="D293">
         <v>3112770503</v>
       </c>
       <c r="E293" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="F293" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="G293">
         <v>74333499</v>
       </c>
       <c r="H293" t="s">
         <v>15</v>
+      </c>
+      <c r="J293" t="s">
+        <v>16</v>
+      </c>
+      <c r="K293" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
